--- a/research/traditional_assets/database/data/serbia/serbia_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_oil_gas_integrated.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1238419339380355</v>
+        <v>0.1236944210371284</v>
       </c>
       <c r="C2">
-        <v>1897.90452012849</v>
+        <v>1882.968021561564</v>
       </c>
       <c r="D2">
-        <v>1512.60452012849</v>
+        <v>1515.469021561564</v>
       </c>
       <c r="E2">
-        <v>-692.1</v>
+        <v>-674.299</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17.801</v>
       </c>
       <c r="G2">
         <v>385.3</v>
@@ -1451,28 +1451,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8953902999999999</v>
       </c>
       <c r="N2">
-        <v>175.1734693877551</v>
+        <v>174.2780790877551</v>
       </c>
       <c r="O2">
-        <v>26.27602040816327</v>
+        <v>26.14171186316327</v>
       </c>
       <c r="P2">
-        <v>148.8974489795918</v>
+        <v>148.1363672245919</v>
       </c>
       <c r="Q2">
-        <v>407.3974489795918</v>
+        <v>406.6363672245918</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1238419339380355</v>
+        <v>0.1245119909465943</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860212</v>
+        <v>0.9429493693913051</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>195.6392306101095</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1236944210371284</v>
+        <v>0.1235469081362214</v>
       </c>
       <c r="C3">
-        <v>1882.968021561564</v>
+        <v>1868.042392903837</v>
       </c>
       <c r="D3">
-        <v>1515.469021561564</v>
+        <v>1518.344392903837</v>
       </c>
       <c r="E3">
-        <v>-674.299</v>
+        <v>-656.498</v>
       </c>
       <c r="F3">
-        <v>17.801</v>
+        <v>35.602</v>
       </c>
       <c r="G3">
         <v>385.3</v>
@@ -1533,28 +1533,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M3">
-        <v>0.8953902999999999</v>
+        <v>1.7907806</v>
       </c>
       <c r="N3">
-        <v>174.2780790877551</v>
+        <v>173.3826887877551</v>
       </c>
       <c r="O3">
-        <v>26.14171186316327</v>
+        <v>26.00740331816327</v>
       </c>
       <c r="P3">
-        <v>148.1363672245919</v>
+        <v>147.3752854695919</v>
       </c>
       <c r="Q3">
-        <v>406.6363672245918</v>
+        <v>405.8752854695919</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1245119909465943</v>
+        <v>0.125195722587981</v>
       </c>
       <c r="T3">
-        <v>0.9429493693913051</v>
+        <v>0.9511402982742482</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>195.6392306101095</v>
+        <v>97.81961530505475</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1235469081362214</v>
+        <v>0.1233993952353143</v>
       </c>
       <c r="C4">
-        <v>1868.042392903837</v>
+        <v>1853.127696144913</v>
       </c>
       <c r="D4">
-        <v>1518.344392903837</v>
+        <v>1521.230696144913</v>
       </c>
       <c r="E4">
-        <v>-656.498</v>
+        <v>-638.697</v>
       </c>
       <c r="F4">
-        <v>35.602</v>
+        <v>53.403</v>
       </c>
       <c r="G4">
         <v>385.3</v>
@@ -1615,28 +1615,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M4">
-        <v>1.7907806</v>
+        <v>2.6861709</v>
       </c>
       <c r="N4">
-        <v>173.3826887877551</v>
+        <v>172.4872984877551</v>
       </c>
       <c r="O4">
-        <v>26.00740331816327</v>
+        <v>25.87309477316327</v>
       </c>
       <c r="P4">
-        <v>147.3752854695919</v>
+        <v>146.6142037145918</v>
       </c>
       <c r="Q4">
-        <v>405.8752854695919</v>
+        <v>405.1142037145918</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.125195722587981</v>
+        <v>0.1258935517889838</v>
       </c>
       <c r="T4">
-        <v>0.9511402982742482</v>
+        <v>0.9595001122887979</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>97.81961530505475</v>
+        <v>65.2130768700365</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1233993952353143</v>
+        <v>0.1232518823344073</v>
       </c>
       <c r="C5">
-        <v>1853.127696144913</v>
+        <v>1838.223993746646</v>
       </c>
       <c r="D5">
-        <v>1521.230696144913</v>
+        <v>1524.127993746646</v>
       </c>
       <c r="E5">
-        <v>-638.697</v>
+        <v>-620.8960000000001</v>
       </c>
       <c r="F5">
-        <v>53.403</v>
+        <v>71.20399999999999</v>
       </c>
       <c r="G5">
         <v>385.3</v>
@@ -1697,28 +1697,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M5">
-        <v>2.6861709</v>
+        <v>3.581561199999999</v>
       </c>
       <c r="N5">
-        <v>172.4872984877551</v>
+        <v>171.5919081877551</v>
       </c>
       <c r="O5">
-        <v>25.87309477316327</v>
+        <v>25.73878622816327</v>
       </c>
       <c r="P5">
-        <v>146.6142037145918</v>
+        <v>145.8531219595918</v>
       </c>
       <c r="Q5">
-        <v>405.1142037145918</v>
+        <v>404.3531219595918</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1258935517889838</v>
+        <v>0.1266059190983409</v>
       </c>
       <c r="T5">
-        <v>0.9595001122887979</v>
+        <v>0.9680340890953177</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.2130768700365</v>
+        <v>48.90980765252738</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1232518823344073</v>
+        <v>0.1231043694335002</v>
       </c>
       <c r="C6">
-        <v>1838.223993746646</v>
+        <v>1823.331348647654</v>
       </c>
       <c r="D6">
-        <v>1524.127993746646</v>
+        <v>1527.036348647654</v>
       </c>
       <c r="E6">
-        <v>-620.8960000000001</v>
+        <v>-603.095</v>
       </c>
       <c r="F6">
-        <v>71.20399999999999</v>
+        <v>89.005</v>
       </c>
       <c r="G6">
         <v>385.3</v>
@@ -1779,28 +1779,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M6">
-        <v>3.581561199999999</v>
+        <v>4.476951499999999</v>
       </c>
       <c r="N6">
-        <v>171.5919081877551</v>
+        <v>170.6965178877551</v>
       </c>
       <c r="O6">
-        <v>25.73878622816327</v>
+        <v>25.60447768316326</v>
       </c>
       <c r="P6">
-        <v>145.8531219595918</v>
+        <v>145.0920402045919</v>
       </c>
       <c r="Q6">
-        <v>404.3531219595918</v>
+        <v>403.5920402045919</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1266059190983409</v>
+        <v>0.1273332836142108</v>
       </c>
       <c r="T6">
-        <v>0.9680340890953177</v>
+        <v>0.9767477285714485</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.90980765252738</v>
+        <v>39.1278461220219</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1231043694335002</v>
+        <v>0.1229568565325932</v>
       </c>
       <c r="C7">
-        <v>1823.331348647654</v>
+        <v>1808.449824267871</v>
       </c>
       <c r="D7">
-        <v>1527.036348647654</v>
+        <v>1529.955824267871</v>
       </c>
       <c r="E7">
-        <v>-603.095</v>
+        <v>-585.294</v>
       </c>
       <c r="F7">
-        <v>89.005</v>
+        <v>106.806</v>
       </c>
       <c r="G7">
         <v>385.3</v>
@@ -1861,28 +1861,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M7">
-        <v>4.476951499999999</v>
+        <v>5.372341799999999</v>
       </c>
       <c r="N7">
-        <v>170.6965178877551</v>
+        <v>169.8011275877551</v>
       </c>
       <c r="O7">
-        <v>25.60447768316326</v>
+        <v>25.47016913816327</v>
       </c>
       <c r="P7">
-        <v>145.0920402045919</v>
+        <v>144.3309584495919</v>
       </c>
       <c r="Q7">
-        <v>403.5920402045919</v>
+        <v>402.8309584495919</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1273332836142108</v>
+        <v>0.1280761239708438</v>
       </c>
       <c r="T7">
-        <v>0.9767477285714485</v>
+        <v>0.9856467646321776</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.1278461220219</v>
+        <v>32.60653843501825</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1229568565325931</v>
+        <v>0.1228093436316861</v>
       </c>
       <c r="C8">
-        <v>1808.449824267871</v>
+        <v>1793.579484513162</v>
       </c>
       <c r="D8">
-        <v>1529.955824267871</v>
+        <v>1532.886484513162</v>
       </c>
       <c r="E8">
-        <v>-585.294</v>
+        <v>-567.4930000000001</v>
       </c>
       <c r="F8">
-        <v>106.806</v>
+        <v>124.607</v>
       </c>
       <c r="G8">
         <v>385.3</v>
@@ -1943,28 +1943,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M8">
-        <v>5.372341799999999</v>
+        <v>6.267732099999999</v>
       </c>
       <c r="N8">
-        <v>169.8011275877551</v>
+        <v>168.9057372877551</v>
       </c>
       <c r="O8">
-        <v>25.47016913816327</v>
+        <v>25.33586059316327</v>
       </c>
       <c r="P8">
-        <v>144.3309584495919</v>
+        <v>143.5698766945919</v>
       </c>
       <c r="Q8">
-        <v>402.8309584495919</v>
+        <v>402.0698766945919</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1280761239708438</v>
+        <v>0.1288349393889098</v>
       </c>
       <c r="T8">
-        <v>0.9856467646321776</v>
+        <v>0.9947371778124925</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.60653843501825</v>
+        <v>27.94846151572993</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1228093436316861</v>
+        <v>0.1226618307307791</v>
       </c>
       <c r="C9">
-        <v>1793.579484513163</v>
+        <v>1778.720393779984</v>
       </c>
       <c r="D9">
-        <v>1532.886484513163</v>
+        <v>1535.828393779984</v>
       </c>
       <c r="E9">
-        <v>-567.4930000000001</v>
+        <v>-549.692</v>
       </c>
       <c r="F9">
-        <v>124.607</v>
+        <v>142.408</v>
       </c>
       <c r="G9">
         <v>385.3</v>
@@ -2025,28 +2025,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M9">
-        <v>6.2677321</v>
+        <v>7.163122399999999</v>
       </c>
       <c r="N9">
-        <v>168.9057372877551</v>
+        <v>168.0103469877551</v>
       </c>
       <c r="O9">
-        <v>25.33586059316327</v>
+        <v>25.20155204816327</v>
       </c>
       <c r="P9">
-        <v>143.5698766945919</v>
+        <v>142.8087949395918</v>
       </c>
       <c r="Q9">
-        <v>402.0698766945919</v>
+        <v>401.3087949395918</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1288349393889098</v>
+        <v>0.1296102507943251</v>
       </c>
       <c r="T9">
-        <v>0.9947371778124925</v>
+        <v>1.00402520867064</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.94846151572993</v>
+        <v>24.45490382626369</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1226618307307791</v>
+        <v>0.122514317829872</v>
       </c>
       <c r="C10">
-        <v>1778.720393779984</v>
+        <v>1763.8726169601</v>
       </c>
       <c r="D10">
-        <v>1535.828393779984</v>
+        <v>1538.7816169601</v>
       </c>
       <c r="E10">
-        <v>-549.692</v>
+        <v>-531.8910000000001</v>
       </c>
       <c r="F10">
-        <v>142.408</v>
+        <v>160.209</v>
       </c>
       <c r="G10">
         <v>385.3</v>
@@ -2107,28 +2107,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M10">
-        <v>7.163122399999999</v>
+        <v>8.058512699999998</v>
       </c>
       <c r="N10">
-        <v>168.0103469877551</v>
+        <v>167.1149566877551</v>
       </c>
       <c r="O10">
-        <v>25.20155204816327</v>
+        <v>25.06724350316327</v>
       </c>
       <c r="P10">
-        <v>142.8087949395918</v>
+        <v>142.0477131845919</v>
       </c>
       <c r="Q10">
-        <v>401.3087949395918</v>
+        <v>400.5477131845919</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1296102507943251</v>
+        <v>0.1304026020108483</v>
       </c>
       <c r="T10">
-        <v>1.00402520867064</v>
+        <v>1.013517372075121</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.45490382626369</v>
+        <v>21.73769229001217</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.122514317829872</v>
+        <v>0.122366804928965</v>
       </c>
       <c r="C11">
-        <v>1763.8726169601</v>
+        <v>1749.036219445351</v>
       </c>
       <c r="D11">
-        <v>1538.7816169601</v>
+        <v>1541.746219445351</v>
       </c>
       <c r="E11">
-        <v>-531.8910000000001</v>
+        <v>-514.09</v>
       </c>
       <c r="F11">
-        <v>160.209</v>
+        <v>178.01</v>
       </c>
       <c r="G11">
         <v>385.3</v>
@@ -2189,28 +2189,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M11">
-        <v>8.058512699999998</v>
+        <v>8.953902999999997</v>
       </c>
       <c r="N11">
-        <v>167.1149566877551</v>
+        <v>166.2195663877551</v>
       </c>
       <c r="O11">
-        <v>25.06724350316327</v>
+        <v>24.93293495816327</v>
       </c>
       <c r="P11">
-        <v>142.0477131845919</v>
+        <v>141.2866314295919</v>
       </c>
       <c r="Q11">
-        <v>400.5477131845919</v>
+        <v>399.7866314295919</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1304026020108483</v>
+        <v>0.1312125610321833</v>
       </c>
       <c r="T11">
-        <v>1.013517372075121</v>
+        <v>1.023220472444146</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.73769229001217</v>
+        <v>19.56392306101096</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.122366804928965</v>
+        <v>0.1222192920280579</v>
       </c>
       <c r="C12">
-        <v>1749.036219445351</v>
+        <v>1734.21126713249</v>
       </c>
       <c r="D12">
-        <v>1541.746219445351</v>
+        <v>1544.72226713249</v>
       </c>
       <c r="E12">
-        <v>-514.09</v>
+        <v>-496.289</v>
       </c>
       <c r="F12">
-        <v>178.01</v>
+        <v>195.811</v>
       </c>
       <c r="G12">
         <v>385.3</v>
@@ -2271,28 +2271,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M12">
-        <v>8.953902999999999</v>
+        <v>9.849293299999998</v>
       </c>
       <c r="N12">
-        <v>166.2195663877551</v>
+        <v>165.3241760877551</v>
       </c>
       <c r="O12">
-        <v>24.93293495816327</v>
+        <v>24.79862641316327</v>
       </c>
       <c r="P12">
-        <v>141.2866314295919</v>
+        <v>140.5255496745918</v>
       </c>
       <c r="Q12">
-        <v>399.7866314295919</v>
+        <v>399.0255496745918</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1312125610321833</v>
+        <v>0.1320407213798403</v>
       </c>
       <c r="T12">
-        <v>1.023220472444146</v>
+        <v>1.033141620012474</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.56392306101095</v>
+        <v>17.78538460091905</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1222192920280579</v>
+        <v>0.1220717791271509</v>
       </c>
       <c r="C13">
-        <v>1734.21126713249</v>
+        <v>1719.397826428053</v>
       </c>
       <c r="D13">
-        <v>1544.72226713249</v>
+        <v>1547.709826428053</v>
       </c>
       <c r="E13">
-        <v>-496.289</v>
+        <v>-478.4880000000001</v>
       </c>
       <c r="F13">
-        <v>195.811</v>
+        <v>213.612</v>
       </c>
       <c r="G13">
         <v>385.3</v>
@@ -2353,28 +2353,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M13">
-        <v>9.849293299999998</v>
+        <v>10.7446836</v>
       </c>
       <c r="N13">
-        <v>165.3241760877551</v>
+        <v>164.4287857877551</v>
       </c>
       <c r="O13">
-        <v>24.79862641316327</v>
+        <v>24.66431786816327</v>
       </c>
       <c r="P13">
-        <v>140.5255496745918</v>
+        <v>139.7644679195919</v>
       </c>
       <c r="Q13">
-        <v>399.0255496745918</v>
+        <v>398.2644679195919</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1320407213798403</v>
+        <v>0.1328877035535805</v>
       </c>
       <c r="T13">
-        <v>1.033141620012474</v>
+        <v>1.043288248207356</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.78538460091905</v>
+        <v>16.30326921750913</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1220717791271509</v>
+        <v>0.1219242662262438</v>
       </c>
       <c r="C14">
-        <v>1719.397826428053</v>
+        <v>1704.595964253306</v>
       </c>
       <c r="D14">
-        <v>1547.709826428053</v>
+        <v>1550.708964253306</v>
       </c>
       <c r="E14">
-        <v>-478.4880000000001</v>
+        <v>-460.687</v>
       </c>
       <c r="F14">
-        <v>213.612</v>
+        <v>231.413</v>
       </c>
       <c r="G14">
         <v>385.3</v>
@@ -2435,28 +2435,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M14">
-        <v>10.7446836</v>
+        <v>11.6400739</v>
       </c>
       <c r="N14">
-        <v>164.4287857877551</v>
+        <v>163.5333954877551</v>
       </c>
       <c r="O14">
-        <v>24.66431786816327</v>
+        <v>24.53000932316327</v>
       </c>
       <c r="P14">
-        <v>139.7644679195919</v>
+        <v>139.0033861645919</v>
       </c>
       <c r="Q14">
-        <v>398.2644679195919</v>
+        <v>397.5033861645919</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1328877035535805</v>
+        <v>0.1337541565818894</v>
       </c>
       <c r="T14">
-        <v>1.043288248207356</v>
+        <v>1.053668132222809</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.30326921750913</v>
+        <v>15.04917158539304</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1219242662262438</v>
+        <v>0.1217767533253367</v>
       </c>
       <c r="C15">
-        <v>1704.595964253306</v>
+        <v>1689.80574804924</v>
       </c>
       <c r="D15">
-        <v>1550.708964253306</v>
+        <v>1553.71974804924</v>
       </c>
       <c r="E15">
-        <v>-460.687</v>
+        <v>-442.886</v>
       </c>
       <c r="F15">
-        <v>231.413</v>
+        <v>249.214</v>
       </c>
       <c r="G15">
         <v>385.3</v>
@@ -2517,28 +2517,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M15">
-        <v>11.6400739</v>
+        <v>12.5354642</v>
       </c>
       <c r="N15">
-        <v>163.5333954877551</v>
+        <v>162.6380051877551</v>
       </c>
       <c r="O15">
-        <v>24.53000932316327</v>
+        <v>24.39570077816327</v>
       </c>
       <c r="P15">
-        <v>139.0033861645919</v>
+        <v>138.2423044095918</v>
       </c>
       <c r="Q15">
-        <v>397.5033861645919</v>
+        <v>396.7423044095918</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1337541565818894</v>
+        <v>0.1346407596806241</v>
       </c>
       <c r="T15">
-        <v>1.053668132222809</v>
+        <v>1.064289408889785</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.04917158539304</v>
+        <v>13.97423075786496</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1217767533253367</v>
+        <v>0.1216292404244297</v>
       </c>
       <c r="C16">
-        <v>1689.80574804924</v>
+        <v>1675.027245781625</v>
       </c>
       <c r="D16">
-        <v>1553.71974804924</v>
+        <v>1556.742245781626</v>
       </c>
       <c r="E16">
-        <v>-442.886</v>
+        <v>-425.085</v>
       </c>
       <c r="F16">
-        <v>249.214</v>
+        <v>267.015</v>
       </c>
       <c r="G16">
         <v>385.3</v>
@@ -2599,28 +2599,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M16">
-        <v>12.5354642</v>
+        <v>13.4308545</v>
       </c>
       <c r="N16">
-        <v>162.6380051877551</v>
+        <v>161.7426148877551</v>
       </c>
       <c r="O16">
-        <v>24.39570077816327</v>
+        <v>24.26139223316327</v>
       </c>
       <c r="P16">
-        <v>138.2423044095918</v>
+        <v>137.4812226545918</v>
       </c>
       <c r="Q16">
-        <v>396.7423044095918</v>
+        <v>395.9812226545919</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1346407596806241</v>
+        <v>0.1355482240287408</v>
       </c>
       <c r="T16">
-        <v>1.064289408889785</v>
+        <v>1.075160597948924</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>13.97423075786496</v>
+        <v>13.0426153740073</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1216292404244297</v>
+        <v>0.1216857275235226</v>
       </c>
       <c r="C17">
-        <v>1675.027245781625</v>
+        <v>1656.067452733585</v>
       </c>
       <c r="D17">
-        <v>1556.742245781626</v>
+        <v>1555.583452733586</v>
       </c>
       <c r="E17">
-        <v>-425.085</v>
+        <v>-407.284</v>
       </c>
       <c r="F17">
-        <v>267.015</v>
+        <v>284.816</v>
       </c>
       <c r="G17">
         <v>385.3</v>
@@ -2681,45 +2681,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M17">
-        <v>13.4308545</v>
+        <v>14.7534688</v>
       </c>
       <c r="N17">
-        <v>161.7426148877551</v>
+        <v>160.4200005877551</v>
       </c>
       <c r="O17">
-        <v>24.26139223316327</v>
+        <v>24.06300008816327</v>
       </c>
       <c r="P17">
-        <v>137.4812226545918</v>
+        <v>136.3570004995918</v>
       </c>
       <c r="Q17">
-        <v>395.9812226545919</v>
+        <v>394.8570004995918</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1355482240287408</v>
+        <v>0.1364772946708603</v>
       </c>
       <c r="T17">
-        <v>1.075160597948924</v>
+        <v>1.086290624842806</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.0426153740073</v>
+        <v>11.87337512028054</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1216857275235226</v>
+        <v>0.1215509646226156</v>
       </c>
       <c r="C18">
-        <v>1656.067452733585</v>
+        <v>1641.033875428964</v>
       </c>
       <c r="D18">
-        <v>1555.583452733586</v>
+        <v>1558.350875428964</v>
       </c>
       <c r="E18">
-        <v>-407.284</v>
+        <v>-389.483</v>
       </c>
       <c r="F18">
-        <v>284.816</v>
+        <v>302.617</v>
       </c>
       <c r="G18">
         <v>385.3</v>
@@ -2763,28 +2763,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M18">
-        <v>14.7534688</v>
+        <v>15.6755606</v>
       </c>
       <c r="N18">
-        <v>160.4200005877551</v>
+        <v>159.4979087877551</v>
       </c>
       <c r="O18">
-        <v>24.06300008816327</v>
+        <v>23.92468631816326</v>
       </c>
       <c r="P18">
-        <v>136.3570004995918</v>
+        <v>135.5732224695919</v>
       </c>
       <c r="Q18">
-        <v>394.8570004995918</v>
+        <v>394.0732224695919</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1364772946708603</v>
+        <v>0.1374287525573682</v>
       </c>
       <c r="T18">
-        <v>1.086290624842806</v>
+        <v>1.097688845155816</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.87337512028054</v>
+        <v>11.1749412896758</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1215509646226156</v>
+        <v>0.1214162017217085</v>
       </c>
       <c r="C19">
-        <v>1641.033875428964</v>
+        <v>1626.010162304292</v>
       </c>
       <c r="D19">
-        <v>1558.350875428964</v>
+        <v>1561.128162304292</v>
       </c>
       <c r="E19">
-        <v>-389.483</v>
+        <v>-371.682</v>
       </c>
       <c r="F19">
-        <v>302.617</v>
+        <v>320.418</v>
       </c>
       <c r="G19">
         <v>385.3</v>
@@ -2845,28 +2845,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M19">
-        <v>15.6755606</v>
+        <v>16.5976524</v>
       </c>
       <c r="N19">
-        <v>159.4979087877551</v>
+        <v>158.5758169877551</v>
       </c>
       <c r="O19">
-        <v>23.92468631816326</v>
+        <v>23.78637254816326</v>
       </c>
       <c r="P19">
-        <v>135.5732224695919</v>
+        <v>134.7894444395918</v>
       </c>
       <c r="Q19">
-        <v>394.0732224695919</v>
+        <v>393.2894444395919</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1374287525573682</v>
+        <v>0.1384034167337909</v>
       </c>
       <c r="T19">
-        <v>1.097688845155816</v>
+        <v>1.109365070842315</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.1749412896758</v>
+        <v>10.55411121802714</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1214162017217085</v>
+        <v>0.1212814388208015</v>
       </c>
       <c r="C20">
-        <v>1626.010162304292</v>
+        <v>1610.996366193439</v>
       </c>
       <c r="D20">
-        <v>1561.128162304292</v>
+        <v>1563.915366193439</v>
       </c>
       <c r="E20">
-        <v>-371.6820000000001</v>
+        <v>-353.881</v>
       </c>
       <c r="F20">
-        <v>320.4179999999999</v>
+        <v>338.219</v>
       </c>
       <c r="G20">
         <v>385.3</v>
@@ -2927,28 +2927,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M20">
-        <v>16.5976524</v>
+        <v>17.5197442</v>
       </c>
       <c r="N20">
-        <v>158.5758169877551</v>
+        <v>157.6537251877551</v>
       </c>
       <c r="O20">
-        <v>23.78637254816327</v>
+        <v>23.64805877816327</v>
       </c>
       <c r="P20">
-        <v>134.7894444395919</v>
+        <v>134.0056664095919</v>
       </c>
       <c r="Q20">
-        <v>393.2894444395919</v>
+        <v>392.5056664095919</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1384034167337909</v>
+        <v>0.1394021466923475</v>
       </c>
       <c r="T20">
-        <v>1.109365070842315</v>
+        <v>1.121329598397617</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.55411121802714</v>
+        <v>9.998631680236242</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1212814388208015</v>
+        <v>0.1214356759198944</v>
       </c>
       <c r="C21">
-        <v>1610.996366193439</v>
+        <v>1590.006212842526</v>
       </c>
       <c r="D21">
-        <v>1563.915366193439</v>
+        <v>1560.726212842526</v>
       </c>
       <c r="E21">
-        <v>-353.881</v>
+        <v>-336.08</v>
       </c>
       <c r="F21">
-        <v>338.219</v>
+        <v>356.02</v>
       </c>
       <c r="G21">
         <v>385.3</v>
@@ -3009,45 +3009,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M21">
-        <v>17.5197442</v>
+        <v>19.04707</v>
       </c>
       <c r="N21">
-        <v>157.6537251877551</v>
+        <v>156.1263993877551</v>
       </c>
       <c r="O21">
-        <v>23.64805877816327</v>
+        <v>23.41895990816327</v>
       </c>
       <c r="P21">
-        <v>134.0056664095919</v>
+        <v>132.7074394795919</v>
       </c>
       <c r="Q21">
-        <v>392.5056664095919</v>
+        <v>391.2074394795919</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1394021466923475</v>
+        <v>0.140425844899868</v>
       </c>
       <c r="T21">
-        <v>1.121329598397617</v>
+        <v>1.133593239141801</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.998631680236242</v>
+        <v>9.196872242699541</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1214356759198944</v>
+        <v>0.1213153630189874</v>
       </c>
       <c r="C22">
-        <v>1590.006212842526</v>
+        <v>1574.691799553915</v>
       </c>
       <c r="D22">
-        <v>1560.726212842526</v>
+        <v>1563.212799553915</v>
       </c>
       <c r="E22">
-        <v>-336.08</v>
+        <v>-318.279</v>
       </c>
       <c r="F22">
-        <v>356.02</v>
+        <v>373.821</v>
       </c>
       <c r="G22">
         <v>385.3</v>
@@ -3091,28 +3091,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M22">
-        <v>19.04707</v>
+        <v>19.9994235</v>
       </c>
       <c r="N22">
-        <v>156.1263993877551</v>
+        <v>155.1740458877551</v>
       </c>
       <c r="O22">
-        <v>23.41895990816327</v>
+        <v>23.27610688316327</v>
       </c>
       <c r="P22">
-        <v>132.7074394795919</v>
+        <v>131.8979390045918</v>
       </c>
       <c r="Q22">
-        <v>391.2074394795919</v>
+        <v>390.3979390045919</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.140425844899868</v>
+        <v>0.1414754595177055</v>
       </c>
       <c r="T22">
-        <v>1.133593239141801</v>
+        <v>1.146167351803559</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.196872242699541</v>
+        <v>8.758925945428132</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1213153630189874</v>
+        <v>0.1211950501180803</v>
       </c>
       <c r="C23">
-        <v>1574.691799553915</v>
+        <v>1559.385322289225</v>
       </c>
       <c r="D23">
-        <v>1563.212799553915</v>
+        <v>1565.707322289225</v>
       </c>
       <c r="E23">
-        <v>-318.2790000000001</v>
+        <v>-300.4780000000001</v>
       </c>
       <c r="F23">
-        <v>373.821</v>
+        <v>391.622</v>
       </c>
       <c r="G23">
         <v>385.3</v>
@@ -3173,28 +3173,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M23">
-        <v>19.9994235</v>
+        <v>20.951777</v>
       </c>
       <c r="N23">
-        <v>155.1740458877551</v>
+        <v>154.2216923877551</v>
       </c>
       <c r="O23">
-        <v>23.27610688316327</v>
+        <v>23.13325385816327</v>
       </c>
       <c r="P23">
-        <v>131.8979390045918</v>
+        <v>131.0884385295919</v>
       </c>
       <c r="Q23">
-        <v>390.3979390045919</v>
+        <v>389.5884385295918</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1414754595177055</v>
+        <v>0.1425519873308722</v>
       </c>
       <c r="T23">
-        <v>1.146167351803559</v>
+        <v>1.15906387761049</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.758925945428132</v>
+        <v>8.360792947908674</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1211950501180803</v>
+        <v>0.1210747372171733</v>
       </c>
       <c r="C24">
-        <v>1559.385322289225</v>
+        <v>1544.086819101303</v>
       </c>
       <c r="D24">
-        <v>1565.707322289225</v>
+        <v>1568.209819101304</v>
       </c>
       <c r="E24">
-        <v>-300.4780000000001</v>
+        <v>-282.677</v>
       </c>
       <c r="F24">
-        <v>391.622</v>
+        <v>409.423</v>
       </c>
       <c r="G24">
         <v>385.3</v>
@@ -3255,28 +3255,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M24">
-        <v>20.951777</v>
+        <v>21.9041305</v>
       </c>
       <c r="N24">
-        <v>154.2216923877551</v>
+        <v>153.2693388877551</v>
       </c>
       <c r="O24">
-        <v>23.13325385816327</v>
+        <v>22.99040083316327</v>
       </c>
       <c r="P24">
-        <v>131.0884385295919</v>
+        <v>130.2789380545918</v>
       </c>
       <c r="Q24">
-        <v>389.5884385295918</v>
+        <v>388.7789380545918</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1425519873308722</v>
+        <v>0.1436564769054198</v>
       </c>
       <c r="T24">
-        <v>1.15906387761049</v>
+        <v>1.172295378113706</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.360792947908674</v>
+        <v>7.997280211043077</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1210747372171733</v>
+        <v>0.1209544243162662</v>
       </c>
       <c r="C25">
-        <v>1544.086819101303</v>
+        <v>1528.796328286671</v>
       </c>
       <c r="D25">
-        <v>1568.209819101304</v>
+        <v>1570.720328286671</v>
       </c>
       <c r="E25">
-        <v>-282.677</v>
+        <v>-264.876</v>
       </c>
       <c r="F25">
-        <v>409.423</v>
+        <v>427.224</v>
       </c>
       <c r="G25">
         <v>385.3</v>
@@ -3337,28 +3337,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M25">
-        <v>21.9041305</v>
+        <v>22.856484</v>
       </c>
       <c r="N25">
-        <v>153.2693388877551</v>
+        <v>152.3169853877551</v>
       </c>
       <c r="O25">
-        <v>22.99040083316327</v>
+        <v>22.84754780816327</v>
       </c>
       <c r="P25">
-        <v>130.2789380545918</v>
+        <v>129.4694375795919</v>
       </c>
       <c r="Q25">
-        <v>388.7789380545918</v>
+        <v>387.9694375795918</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1436564769054198</v>
+        <v>0.1447900319950871</v>
       </c>
       <c r="T25">
-        <v>1.172295378113706</v>
+        <v>1.185875075998585</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.997280211043077</v>
+        <v>7.664060202249617</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1209544243162662</v>
+        <v>0.1210041114153591</v>
       </c>
       <c r="C26">
-        <v>1528.796328286671</v>
+        <v>1509.957558740165</v>
       </c>
       <c r="D26">
-        <v>1570.720328286671</v>
+        <v>1569.682558740166</v>
       </c>
       <c r="E26">
-        <v>-264.876</v>
+        <v>-247.075</v>
       </c>
       <c r="F26">
-        <v>427.224</v>
+        <v>445.025</v>
       </c>
       <c r="G26">
         <v>385.3</v>
@@ -3419,45 +3419,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M26">
-        <v>22.856484</v>
+        <v>24.1648575</v>
       </c>
       <c r="N26">
-        <v>152.3169853877551</v>
+        <v>151.0086118877551</v>
       </c>
       <c r="O26">
-        <v>22.84754780816327</v>
+        <v>22.65129178316327</v>
       </c>
       <c r="P26">
-        <v>129.4694375795919</v>
+        <v>128.3573201045918</v>
       </c>
       <c r="Q26">
-        <v>387.9694375795918</v>
+        <v>386.8573201045918</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1447900319950871</v>
+        <v>0.1459538152204788</v>
       </c>
       <c r="T26">
-        <v>1.185875075998585</v>
+        <v>1.199816899160394</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.664060202249617</v>
+        <v>7.249100036602951</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1210041114153591</v>
+        <v>0.1208905985144521</v>
       </c>
       <c r="C27">
-        <v>1509.957558740165</v>
+        <v>1494.529415319694</v>
       </c>
       <c r="D27">
-        <v>1569.682558740166</v>
+        <v>1572.055415319694</v>
       </c>
       <c r="E27">
-        <v>-247.075</v>
+        <v>-229.2740000000001</v>
       </c>
       <c r="F27">
-        <v>445.025</v>
+        <v>462.826</v>
       </c>
       <c r="G27">
         <v>385.3</v>
@@ -3501,28 +3501,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M27">
-        <v>24.1648575</v>
+        <v>25.1314518</v>
       </c>
       <c r="N27">
-        <v>151.0086118877551</v>
+        <v>150.0420175877551</v>
       </c>
       <c r="O27">
-        <v>22.65129178316327</v>
+        <v>22.50630263816327</v>
       </c>
       <c r="P27">
-        <v>128.3573201045918</v>
+        <v>127.5357149495918</v>
       </c>
       <c r="Q27">
-        <v>386.8573201045918</v>
+        <v>386.0357149495919</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1459538152204788</v>
+        <v>0.1471490520465569</v>
       </c>
       <c r="T27">
-        <v>1.199816899160394</v>
+        <v>1.214135528353603</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.249100036602951</v>
+        <v>6.970288496733608</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1208905985144521</v>
+        <v>0.1207770856135451</v>
       </c>
       <c r="C28">
-        <v>1494.529415319694</v>
+        <v>1479.108456756612</v>
       </c>
       <c r="D28">
-        <v>1572.055415319694</v>
+        <v>1574.435456756612</v>
       </c>
       <c r="E28">
-        <v>-229.2740000000001</v>
+        <v>-211.473</v>
       </c>
       <c r="F28">
-        <v>462.826</v>
+        <v>480.627</v>
       </c>
       <c r="G28">
         <v>385.3</v>
@@ -3583,28 +3583,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M28">
-        <v>25.1314518</v>
+        <v>26.0980461</v>
       </c>
       <c r="N28">
-        <v>150.0420175877551</v>
+        <v>149.0754232877551</v>
       </c>
       <c r="O28">
-        <v>22.50630263816327</v>
+        <v>22.36131349316327</v>
       </c>
       <c r="P28">
-        <v>127.5357149495918</v>
+        <v>126.7141097945918</v>
       </c>
       <c r="Q28">
-        <v>386.0357149495919</v>
+        <v>385.2141097945919</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1471490520465569</v>
+        <v>0.148377035087048</v>
       </c>
       <c r="T28">
-        <v>1.214135528353603</v>
+        <v>1.228846448757586</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.970288496733608</v>
+        <v>6.712129663521251</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1207770856135451</v>
+        <v>0.120663572712638</v>
       </c>
       <c r="C29">
-        <v>1479.108456756612</v>
+        <v>1463.694715733329</v>
       </c>
       <c r="D29">
-        <v>1574.435456756612</v>
+        <v>1576.822715733329</v>
       </c>
       <c r="E29">
-        <v>-211.473</v>
+        <v>-193.672</v>
       </c>
       <c r="F29">
-        <v>480.627</v>
+        <v>498.428</v>
       </c>
       <c r="G29">
         <v>385.3</v>
@@ -3665,28 +3665,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M29">
-        <v>26.0980461</v>
+        <v>27.0646404</v>
       </c>
       <c r="N29">
-        <v>149.0754232877551</v>
+        <v>148.1088289877551</v>
       </c>
       <c r="O29">
-        <v>22.36131349316327</v>
+        <v>22.21632434816327</v>
       </c>
       <c r="P29">
-        <v>126.7141097945918</v>
+        <v>125.8925046395918</v>
       </c>
       <c r="Q29">
-        <v>385.2141097945919</v>
+        <v>384.3925046395918</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.148377035087048</v>
+        <v>0.1496391287675528</v>
       </c>
       <c r="T29">
-        <v>1.228846448757586</v>
+        <v>1.243966005839456</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.712129663521251</v>
+        <v>6.472410746966921</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.120663572712638</v>
+        <v>0.1205500598117309</v>
       </c>
       <c r="C30">
-        <v>1463.694715733329</v>
+        <v>1448.288225130778</v>
       </c>
       <c r="D30">
-        <v>1576.822715733329</v>
+        <v>1579.217225130778</v>
       </c>
       <c r="E30">
-        <v>-193.672</v>
+        <v>-175.871</v>
       </c>
       <c r="F30">
-        <v>498.428</v>
+        <v>516.229</v>
       </c>
       <c r="G30">
         <v>385.3</v>
@@ -3747,28 +3747,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M30">
-        <v>27.0646404</v>
+        <v>28.0312347</v>
       </c>
       <c r="N30">
-        <v>148.1088289877551</v>
+        <v>147.1422346877551</v>
       </c>
       <c r="O30">
-        <v>22.21632434816327</v>
+        <v>22.07133520316327</v>
       </c>
       <c r="P30">
-        <v>125.8925046395918</v>
+        <v>125.0708994845918</v>
       </c>
       <c r="Q30">
-        <v>384.3925046395918</v>
+        <v>383.5708994845918</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1496391287675528</v>
+        <v>0.1509367743827196</v>
       </c>
       <c r="T30">
-        <v>1.243966005839456</v>
+        <v>1.259511465937717</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.472410746966921</v>
+        <v>6.249224169485303</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1205500598117309</v>
+        <v>0.1206915469108239</v>
       </c>
       <c r="C31">
-        <v>1448.288225130778</v>
+        <v>1427.50372601455</v>
       </c>
       <c r="D31">
-        <v>1579.217225130778</v>
+        <v>1576.23372601455</v>
       </c>
       <c r="E31">
-        <v>-175.8710000000001</v>
+        <v>-158.0700000000001</v>
       </c>
       <c r="F31">
-        <v>516.2289999999999</v>
+        <v>534.03</v>
       </c>
       <c r="G31">
         <v>385.3</v>
@@ -3829,45 +3829,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M31">
-        <v>28.0312347</v>
+        <v>29.531859</v>
       </c>
       <c r="N31">
-        <v>147.1422346877551</v>
+        <v>145.6416103877551</v>
       </c>
       <c r="O31">
-        <v>22.07133520316327</v>
+        <v>21.84624155816327</v>
       </c>
       <c r="P31">
-        <v>125.0708994845918</v>
+        <v>123.7953688295919</v>
       </c>
       <c r="Q31">
-        <v>383.5708994845918</v>
+        <v>382.2953688295918</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1509367743827196</v>
+        <v>0.1522714955868913</v>
       </c>
       <c r="T31">
-        <v>1.259511465937717</v>
+        <v>1.275501082038786</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.249224169485305</v>
+        <v>5.931677697220318</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1206915469108239</v>
+        <v>0.1205865340099168</v>
       </c>
       <c r="C32">
-        <v>1427.50372601455</v>
+        <v>1411.916023879837</v>
       </c>
       <c r="D32">
-        <v>1576.23372601455</v>
+        <v>1578.447023879837</v>
       </c>
       <c r="E32">
-        <v>-158.0700000000001</v>
+        <v>-140.269</v>
       </c>
       <c r="F32">
-        <v>534.03</v>
+        <v>551.831</v>
       </c>
       <c r="G32">
         <v>385.3</v>
@@ -3911,28 +3911,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M32">
-        <v>29.531859</v>
+        <v>30.5162543</v>
       </c>
       <c r="N32">
-        <v>145.6416103877551</v>
+        <v>144.6572150877551</v>
       </c>
       <c r="O32">
-        <v>21.84624155816327</v>
+        <v>21.69858226316326</v>
       </c>
       <c r="P32">
-        <v>123.7953688295919</v>
+        <v>122.9586328245918</v>
       </c>
       <c r="Q32">
-        <v>382.2953688295918</v>
+        <v>381.4586328245919</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1522714955868913</v>
+        <v>0.1536449043621983</v>
       </c>
       <c r="T32">
-        <v>1.275501082038786</v>
+        <v>1.291954165273219</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.931677697220318</v>
+        <v>5.7403332553745</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1205865340099168</v>
+        <v>0.1204815211090098</v>
       </c>
       <c r="C33">
-        <v>1411.916023879837</v>
+        <v>1396.334546171889</v>
       </c>
       <c r="D33">
-        <v>1578.447023879837</v>
+        <v>1580.666546171889</v>
       </c>
       <c r="E33">
-        <v>-140.269</v>
+        <v>-122.4680000000001</v>
       </c>
       <c r="F33">
-        <v>551.831</v>
+        <v>569.6319999999999</v>
       </c>
       <c r="G33">
         <v>385.3</v>
@@ -3993,28 +3993,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M33">
-        <v>30.5162543</v>
+        <v>31.5006496</v>
       </c>
       <c r="N33">
-        <v>144.6572150877551</v>
+        <v>143.6728197877551</v>
       </c>
       <c r="O33">
-        <v>21.69858226316326</v>
+        <v>21.55092296816327</v>
       </c>
       <c r="P33">
-        <v>122.9586328245918</v>
+        <v>122.1218968195919</v>
       </c>
       <c r="Q33">
-        <v>381.4586328245919</v>
+        <v>380.6218968195918</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1536449043621983</v>
+        <v>0.1550587075132497</v>
       </c>
       <c r="T33">
-        <v>1.291954165273219</v>
+        <v>1.30889116272043</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.7403332553745</v>
+        <v>5.560947841144048</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1204815211090098</v>
+        <v>0.1203765082081027</v>
       </c>
       <c r="C34">
-        <v>1396.334546171889</v>
+        <v>1380.759319184981</v>
       </c>
       <c r="D34">
-        <v>1580.666546171889</v>
+        <v>1582.892319184981</v>
       </c>
       <c r="E34">
-        <v>-122.4680000000001</v>
+        <v>-104.667</v>
       </c>
       <c r="F34">
-        <v>569.6319999999999</v>
+        <v>587.433</v>
       </c>
       <c r="G34">
         <v>385.3</v>
@@ -4075,28 +4075,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M34">
-        <v>31.5006496</v>
+        <v>32.4850449</v>
       </c>
       <c r="N34">
-        <v>143.6728197877551</v>
+        <v>142.6884244877551</v>
       </c>
       <c r="O34">
-        <v>21.55092296816327</v>
+        <v>21.40326367316327</v>
       </c>
       <c r="P34">
-        <v>122.1218968195919</v>
+        <v>121.2851608145919</v>
       </c>
       <c r="Q34">
-        <v>380.6218968195918</v>
+        <v>379.7851608145918</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1550587075132497</v>
+        <v>0.1565147137434369</v>
       </c>
       <c r="T34">
-        <v>1.30889116272043</v>
+        <v>1.32633374218099</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.560947841144048</v>
+        <v>5.392434270200289</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1203765082081027</v>
+        <v>0.1202714953071956</v>
       </c>
       <c r="C35">
-        <v>1380.759319184981</v>
+        <v>1365.190369361701</v>
       </c>
       <c r="D35">
-        <v>1582.892319184981</v>
+        <v>1585.124369361702</v>
       </c>
       <c r="E35">
-        <v>-104.667</v>
+        <v>-86.86599999999999</v>
       </c>
       <c r="F35">
-        <v>587.433</v>
+        <v>605.234</v>
       </c>
       <c r="G35">
         <v>385.3</v>
@@ -4157,28 +4157,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M35">
-        <v>32.4850449</v>
+        <v>33.4694402</v>
       </c>
       <c r="N35">
-        <v>142.6884244877551</v>
+        <v>141.7040291877551</v>
       </c>
       <c r="O35">
-        <v>21.40326367316327</v>
+        <v>21.25560437816327</v>
       </c>
       <c r="P35">
-        <v>121.2851608145919</v>
+        <v>120.4484248095918</v>
       </c>
       <c r="Q35">
-        <v>379.7851608145918</v>
+        <v>378.9484248095919</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1565147137434369</v>
+        <v>0.1580148413745389</v>
       </c>
       <c r="T35">
-        <v>1.32633374218099</v>
+        <v>1.344304884655506</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.392434270200289</v>
+        <v>5.233833262253222</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1202714953071956</v>
+        <v>0.1201664824062886</v>
       </c>
       <c r="C36">
-        <v>1365.190369361701</v>
+        <v>1349.627723293997</v>
       </c>
       <c r="D36">
-        <v>1585.124369361702</v>
+        <v>1587.362723293997</v>
       </c>
       <c r="E36">
-        <v>-86.86599999999999</v>
+        <v>-69.06499999999994</v>
       </c>
       <c r="F36">
-        <v>605.234</v>
+        <v>623.0350000000001</v>
       </c>
       <c r="G36">
         <v>385.3</v>
@@ -4239,28 +4239,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M36">
-        <v>33.4694402</v>
+        <v>34.4538355</v>
       </c>
       <c r="N36">
-        <v>141.7040291877551</v>
+        <v>140.7196338877551</v>
       </c>
       <c r="O36">
-        <v>21.25560437816327</v>
+        <v>21.10794508316327</v>
       </c>
       <c r="P36">
-        <v>120.4484248095918</v>
+        <v>119.6116888045919</v>
       </c>
       <c r="Q36">
-        <v>378.9484248095919</v>
+        <v>378.1116888045918</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1580148413745389</v>
+        <v>0.1595611267789056</v>
       </c>
       <c r="T36">
-        <v>1.344304884655506</v>
+        <v>1.362828985360008</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.233833262253222</v>
+        <v>5.084295169045986</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1201664824062886</v>
+        <v>0.1200614695053816</v>
       </c>
       <c r="C37">
-        <v>1349.627723293997</v>
+        <v>1334.071407724228</v>
       </c>
       <c r="D37">
-        <v>1587.362723293997</v>
+        <v>1589.607407724229</v>
       </c>
       <c r="E37">
-        <v>-69.06499999999994</v>
+        <v>-51.26400000000001</v>
       </c>
       <c r="F37">
-        <v>623.0350000000001</v>
+        <v>640.836</v>
       </c>
       <c r="G37">
         <v>385.3</v>
@@ -4321,28 +4321,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M37">
-        <v>34.4538355</v>
+        <v>35.4382308</v>
       </c>
       <c r="N37">
-        <v>140.7196338877551</v>
+        <v>139.7352385877551</v>
       </c>
       <c r="O37">
-        <v>21.10794508316327</v>
+        <v>20.96028578816327</v>
       </c>
       <c r="P37">
-        <v>119.6116888045919</v>
+        <v>118.7749527995919</v>
       </c>
       <c r="Q37">
-        <v>378.1116888045918</v>
+        <v>377.2749527995919</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1595611267789056</v>
+        <v>0.1611557336021587</v>
       </c>
       <c r="T37">
-        <v>1.362828985360008</v>
+        <v>1.381931964211525</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.084295169045986</v>
+        <v>4.943064747683598</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1200614695053816</v>
+        <v>0.1199564566044745</v>
       </c>
       <c r="C38">
-        <v>1334.071407724229</v>
+        <v>1318.521449546235</v>
       </c>
       <c r="D38">
-        <v>1589.607407724229</v>
+        <v>1591.858449546235</v>
       </c>
       <c r="E38">
-        <v>-51.26400000000012</v>
+        <v>-33.46300000000008</v>
       </c>
       <c r="F38">
-        <v>640.8359999999999</v>
+        <v>658.6369999999999</v>
       </c>
       <c r="G38">
         <v>385.3</v>
@@ -4403,28 +4403,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M38">
-        <v>35.43823079999999</v>
+        <v>36.4226261</v>
       </c>
       <c r="N38">
-        <v>139.7352385877551</v>
+        <v>138.7508432877551</v>
       </c>
       <c r="O38">
-        <v>20.96028578816327</v>
+        <v>20.81262649316327</v>
       </c>
       <c r="P38">
-        <v>118.7749527995919</v>
+        <v>117.9382167945919</v>
       </c>
       <c r="Q38">
-        <v>377.2749527995919</v>
+        <v>376.4382167945919</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1611557336021587</v>
+        <v>0.1628009628642453</v>
       </c>
       <c r="T38">
-        <v>1.381931964211525</v>
+        <v>1.401641386836106</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.9430647476836</v>
+        <v>4.80946840315161</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1199564566044745</v>
+        <v>0.1198514437035675</v>
       </c>
       <c r="C39">
-        <v>1318.521449546235</v>
+        <v>1302.977875806409</v>
       </c>
       <c r="D39">
-        <v>1591.858449546235</v>
+        <v>1594.115875806409</v>
       </c>
       <c r="E39">
-        <v>-33.46300000000008</v>
+        <v>-15.66200000000003</v>
       </c>
       <c r="F39">
-        <v>658.6369999999999</v>
+        <v>676.438</v>
       </c>
       <c r="G39">
         <v>385.3</v>
@@ -4485,28 +4485,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M39">
-        <v>36.4226261</v>
+        <v>37.4070214</v>
       </c>
       <c r="N39">
-        <v>138.7508432877551</v>
+        <v>137.7664479877551</v>
       </c>
       <c r="O39">
-        <v>20.81262649316327</v>
+        <v>20.66496719816327</v>
       </c>
       <c r="P39">
-        <v>117.9382167945919</v>
+        <v>117.1014807895919</v>
       </c>
       <c r="Q39">
-        <v>376.4382167945919</v>
+        <v>375.6014807895918</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1628009628642453</v>
+        <v>0.164499264038012</v>
       </c>
       <c r="T39">
-        <v>1.401641386836106</v>
+        <v>1.421986597287287</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.80946840315161</v>
+        <v>4.682903445173936</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1198514437035675</v>
+        <v>0.1197464308026604</v>
       </c>
       <c r="C40">
-        <v>1302.977875806409</v>
+        <v>1287.440713704781</v>
       </c>
       <c r="D40">
-        <v>1594.115875806409</v>
+        <v>1596.379713704781</v>
       </c>
       <c r="E40">
-        <v>-15.66200000000003</v>
+        <v>2.13900000000001</v>
       </c>
       <c r="F40">
-        <v>676.438</v>
+        <v>694.239</v>
       </c>
       <c r="G40">
         <v>385.3</v>
@@ -4567,28 +4567,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M40">
-        <v>37.4070214</v>
+        <v>38.3914167</v>
       </c>
       <c r="N40">
-        <v>137.7664479877551</v>
+        <v>136.7820526877551</v>
       </c>
       <c r="O40">
-        <v>20.66496719816327</v>
+        <v>20.51730790316327</v>
       </c>
       <c r="P40">
-        <v>117.1014807895919</v>
+        <v>116.2647447845918</v>
       </c>
       <c r="Q40">
-        <v>375.6014807895918</v>
+        <v>374.7647447845918</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.164499264038012</v>
+        <v>0.1662532472174761</v>
       </c>
       <c r="T40">
-        <v>1.421986597287287</v>
+        <v>1.442998863818834</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.682903445173936</v>
+        <v>4.562828997861782</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1197464308026604</v>
+        <v>0.1204914179017533</v>
       </c>
       <c r="C41">
-        <v>1287.440713704781</v>
+        <v>1253.717104047965</v>
       </c>
       <c r="D41">
-        <v>1596.379713704781</v>
+        <v>1580.457104047965</v>
       </c>
       <c r="E41">
-        <v>2.13900000000001</v>
+        <v>19.93999999999994</v>
       </c>
       <c r="F41">
-        <v>694.239</v>
+        <v>712.04</v>
       </c>
       <c r="G41">
         <v>385.3</v>
@@ -4649,45 +4649,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M41">
-        <v>38.3914167</v>
+        <v>41.155912</v>
       </c>
       <c r="N41">
-        <v>136.7820526877551</v>
+        <v>134.0175573877551</v>
       </c>
       <c r="O41">
-        <v>20.51730790316327</v>
+        <v>20.10263360816327</v>
       </c>
       <c r="P41">
-        <v>116.2647447845918</v>
+        <v>113.9149237795918</v>
       </c>
       <c r="Q41">
-        <v>374.7647447845918</v>
+        <v>372.4149237795918</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1662532472174761</v>
+        <v>0.1680656965029222</v>
       </c>
       <c r="T41">
-        <v>1.442998863818834</v>
+        <v>1.464711539234767</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.15</v>
       </c>
       <c r="W41">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.562828997861782</v>
+        <v>4.256337932391222</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1204914179017533</v>
+        <v>0.1204076550008463</v>
       </c>
       <c r="C42">
-        <v>1253.717104047965</v>
+        <v>1237.690502020837</v>
       </c>
       <c r="D42">
-        <v>1580.457104047965</v>
+        <v>1582.231502020837</v>
       </c>
       <c r="E42">
-        <v>19.93999999999994</v>
+        <v>37.74099999999999</v>
       </c>
       <c r="F42">
-        <v>712.04</v>
+        <v>729.841</v>
       </c>
       <c r="G42">
         <v>385.3</v>
@@ -4731,28 +4731,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M42">
-        <v>41.155912</v>
+        <v>42.1848098</v>
       </c>
       <c r="N42">
-        <v>134.0175573877551</v>
+        <v>132.9886595877551</v>
       </c>
       <c r="O42">
-        <v>20.10263360816327</v>
+        <v>19.94829893816327</v>
       </c>
       <c r="P42">
-        <v>113.9149237795918</v>
+        <v>113.0403606495918</v>
       </c>
       <c r="Q42">
-        <v>372.4149237795918</v>
+        <v>371.5403606495918</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1680656965029222</v>
+        <v>0.1699395847471971</v>
       </c>
       <c r="T42">
-        <v>1.464711539234767</v>
+        <v>1.487160237546154</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.256337932391222</v>
+        <v>4.152524812088997</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1204076550008463</v>
+        <v>0.1203238920999392</v>
       </c>
       <c r="C43">
-        <v>1237.690502020837</v>
+        <v>1221.667888747312</v>
       </c>
       <c r="D43">
-        <v>1582.231502020837</v>
+        <v>1584.009888747312</v>
       </c>
       <c r="E43">
-        <v>37.74099999999999</v>
+        <v>55.54200000000003</v>
       </c>
       <c r="F43">
-        <v>729.841</v>
+        <v>747.6420000000001</v>
       </c>
       <c r="G43">
         <v>385.3</v>
@@ -4813,28 +4813,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M43">
-        <v>42.1848098</v>
+        <v>43.21370760000001</v>
       </c>
       <c r="N43">
-        <v>132.9886595877551</v>
+        <v>131.9597617877551</v>
       </c>
       <c r="O43">
-        <v>19.94829893816327</v>
+        <v>19.79396426816326</v>
       </c>
       <c r="P43">
-        <v>113.0403606495918</v>
+        <v>112.1657975195918</v>
       </c>
       <c r="Q43">
-        <v>371.5403606495918</v>
+        <v>370.6657975195918</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1699395847471971</v>
+        <v>0.1718780898274815</v>
       </c>
       <c r="T43">
-        <v>1.487160237546154</v>
+        <v>1.510383028902762</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.152524812088997</v>
+        <v>4.053655173705925</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1203238920999393</v>
+        <v>0.1215193791990322</v>
       </c>
       <c r="C44">
-        <v>1221.667888747312</v>
+        <v>1178.857922656142</v>
       </c>
       <c r="D44">
-        <v>1584.009888747312</v>
+        <v>1559.000922656142</v>
       </c>
       <c r="E44">
-        <v>55.54199999999992</v>
+        <v>73.34299999999996</v>
       </c>
       <c r="F44">
-        <v>747.6419999999999</v>
+        <v>765.443</v>
       </c>
       <c r="G44">
         <v>385.3</v>
@@ -4895,45 +4895,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M44">
-        <v>43.2137076</v>
+        <v>46.9216559</v>
       </c>
       <c r="N44">
-        <v>131.9597617877551</v>
+        <v>128.2518134877551</v>
       </c>
       <c r="O44">
-        <v>19.79396426816327</v>
+        <v>19.23777202316327</v>
       </c>
       <c r="P44">
-        <v>112.1657975195919</v>
+        <v>109.0140414645919</v>
       </c>
       <c r="Q44">
-        <v>370.6657975195919</v>
+        <v>367.5140414645919</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1718780898274815</v>
+        <v>0.173884612629881</v>
       </c>
       <c r="T44">
-        <v>1.510383028902762</v>
+        <v>1.534420655043812</v>
       </c>
       <c r="U44">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V44">
         <v>0.15</v>
       </c>
       <c r="W44">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.053655173705927</v>
+        <v>3.733318145486744</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1215193791990322</v>
+        <v>0.1214653662981251</v>
       </c>
       <c r="C45">
-        <v>1178.857922656142</v>
+        <v>1162.169798552594</v>
       </c>
       <c r="D45">
-        <v>1559.000922656142</v>
+        <v>1560.113798552594</v>
       </c>
       <c r="E45">
-        <v>73.34299999999996</v>
+        <v>91.14399999999989</v>
       </c>
       <c r="F45">
-        <v>765.443</v>
+        <v>783.2439999999999</v>
       </c>
       <c r="G45">
         <v>385.3</v>
@@ -4977,28 +4977,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M45">
-        <v>46.9216559</v>
+        <v>48.01285719999999</v>
       </c>
       <c r="N45">
-        <v>128.2518134877551</v>
+        <v>127.1606121877551</v>
       </c>
       <c r="O45">
-        <v>19.23777202316327</v>
+        <v>19.07409182816327</v>
       </c>
       <c r="P45">
-        <v>109.0140414645919</v>
+        <v>108.0865203595919</v>
       </c>
       <c r="Q45">
-        <v>367.5140414645919</v>
+        <v>366.5865203595919</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.173884612629881</v>
+        <v>0.1759627969609377</v>
       </c>
       <c r="T45">
-        <v>1.534420655043812</v>
+        <v>1.559316767832757</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.733318145486744</v>
+        <v>3.648470005816591</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1214653662981251</v>
+        <v>0.1214113533972181</v>
       </c>
       <c r="C46">
-        <v>1162.169798552594</v>
+        <v>1145.483264412797</v>
       </c>
       <c r="D46">
-        <v>1560.113798552594</v>
+        <v>1561.228264412797</v>
       </c>
       <c r="E46">
-        <v>91.14399999999989</v>
+        <v>108.9449999999999</v>
       </c>
       <c r="F46">
-        <v>783.2439999999999</v>
+        <v>801.045</v>
       </c>
       <c r="G46">
         <v>385.3</v>
@@ -5059,28 +5059,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M46">
-        <v>48.01285719999999</v>
+        <v>49.1040585</v>
       </c>
       <c r="N46">
-        <v>127.1606121877551</v>
+        <v>126.0694108877551</v>
       </c>
       <c r="O46">
-        <v>19.07409182816327</v>
+        <v>18.91041163316327</v>
       </c>
       <c r="P46">
-        <v>108.0865203595919</v>
+        <v>107.1589992545918</v>
       </c>
       <c r="Q46">
-        <v>366.5865203595919</v>
+        <v>365.6589992545918</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1759627969609377</v>
+        <v>0.1781165516313056</v>
       </c>
       <c r="T46">
-        <v>1.559316767832757</v>
+        <v>1.585118193814027</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.648470005816591</v>
+        <v>3.567392894576221</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1214113533972181</v>
+        <v>0.1224521404963111</v>
       </c>
       <c r="C47">
-        <v>1145.483264412797</v>
+        <v>1106.483818735753</v>
       </c>
       <c r="D47">
-        <v>1561.228264412797</v>
+        <v>1540.029818735753</v>
       </c>
       <c r="E47">
-        <v>108.9449999999999</v>
+        <v>126.746</v>
       </c>
       <c r="F47">
-        <v>801.045</v>
+        <v>818.846</v>
       </c>
       <c r="G47">
         <v>385.3</v>
@@ -5141,45 +5141,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M47">
-        <v>49.1040585</v>
+        <v>52.48802860000001</v>
       </c>
       <c r="N47">
-        <v>126.0694108877551</v>
+        <v>122.6854407877551</v>
       </c>
       <c r="O47">
-        <v>18.91041163316327</v>
+        <v>18.40281611816327</v>
       </c>
       <c r="P47">
-        <v>107.1589992545918</v>
+        <v>104.2826246695919</v>
       </c>
       <c r="Q47">
-        <v>365.6589992545918</v>
+        <v>362.7826246695919</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1781165516313056</v>
+        <v>0.1803500749931686</v>
       </c>
       <c r="T47">
-        <v>1.585118193814027</v>
+        <v>1.611875228164974</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.15</v>
       </c>
       <c r="W47">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.567392894576221</v>
+        <v>3.337398528009397</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1224521404963111</v>
+        <v>0.122421927595404</v>
       </c>
       <c r="C48">
-        <v>1106.483818735753</v>
+        <v>1089.29007007708</v>
       </c>
       <c r="D48">
-        <v>1540.029818735753</v>
+        <v>1540.63707007708</v>
       </c>
       <c r="E48">
-        <v>126.746</v>
+        <v>144.547</v>
       </c>
       <c r="F48">
-        <v>818.846</v>
+        <v>836.647</v>
       </c>
       <c r="G48">
         <v>385.3</v>
@@ -5223,28 +5223,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M48">
-        <v>52.48802860000001</v>
+        <v>53.62907270000001</v>
       </c>
       <c r="N48">
-        <v>122.6854407877551</v>
+        <v>121.5443966877551</v>
       </c>
       <c r="O48">
-        <v>18.40281611816327</v>
+        <v>18.23165950316326</v>
       </c>
       <c r="P48">
-        <v>104.2826246695919</v>
+        <v>103.3127371845918</v>
       </c>
       <c r="Q48">
-        <v>362.7826246695919</v>
+        <v>361.8127371845918</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1803500749931686</v>
+        <v>0.1826678822554792</v>
       </c>
       <c r="T48">
-        <v>1.611875228164974</v>
+        <v>1.63964196192539</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.337398528009397</v>
+        <v>3.266390048690047</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.122421927595404</v>
+        <v>0.1223917146944969</v>
       </c>
       <c r="C49">
-        <v>1089.29007007708</v>
+        <v>1072.09680049959</v>
       </c>
       <c r="D49">
-        <v>1540.63707007708</v>
+        <v>1541.24480049959</v>
       </c>
       <c r="E49">
-        <v>144.547</v>
+        <v>162.348</v>
       </c>
       <c r="F49">
-        <v>836.647</v>
+        <v>854.448</v>
       </c>
       <c r="G49">
         <v>385.3</v>
@@ -5305,28 +5305,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M49">
-        <v>53.62907270000001</v>
+        <v>54.7701168</v>
       </c>
       <c r="N49">
-        <v>121.5443966877551</v>
+        <v>120.4033525877551</v>
       </c>
       <c r="O49">
-        <v>18.23165950316326</v>
+        <v>18.06050288816327</v>
       </c>
       <c r="P49">
-        <v>103.3127371845918</v>
+        <v>102.3428496995918</v>
       </c>
       <c r="Q49">
-        <v>361.8127371845918</v>
+        <v>360.8428496995919</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1826678822554792</v>
+        <v>0.1850748359509556</v>
       </c>
       <c r="T49">
-        <v>1.63964196192539</v>
+        <v>1.668476646984284</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.266390048690047</v>
+        <v>3.198340256009005</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1223917146944969</v>
+        <v>0.1223615017935899</v>
       </c>
       <c r="C50">
-        <v>1072.09680049959</v>
+        <v>1054.90401057045</v>
       </c>
       <c r="D50">
-        <v>1541.24480049959</v>
+        <v>1541.85301057045</v>
       </c>
       <c r="E50">
-        <v>162.348</v>
+        <v>180.1489999999999</v>
       </c>
       <c r="F50">
-        <v>854.448</v>
+        <v>872.2489999999999</v>
       </c>
       <c r="G50">
         <v>385.3</v>
@@ -5387,28 +5387,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M50">
-        <v>54.7701168</v>
+        <v>55.9111609</v>
       </c>
       <c r="N50">
-        <v>120.4033525877551</v>
+        <v>119.2623084877551</v>
       </c>
       <c r="O50">
-        <v>18.06050288816327</v>
+        <v>17.88934627316327</v>
       </c>
       <c r="P50">
-        <v>102.3428496995918</v>
+        <v>101.3729622145919</v>
       </c>
       <c r="Q50">
-        <v>360.8428496995919</v>
+        <v>359.8729622145918</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1850748359509556</v>
+        <v>0.1875761799874311</v>
       </c>
       <c r="T50">
-        <v>1.668476646984284</v>
+        <v>1.698442104006272</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.198340256009005</v>
+        <v>3.133068005886372</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1223615017935899</v>
+        <v>0.1223312888926828</v>
       </c>
       <c r="C51">
-        <v>1054.90401057045</v>
+        <v>1037.711700857724</v>
       </c>
       <c r="D51">
-        <v>1541.85301057045</v>
+        <v>1542.461700857724</v>
       </c>
       <c r="E51">
-        <v>180.1489999999999</v>
+        <v>197.9499999999999</v>
       </c>
       <c r="F51">
-        <v>872.2489999999999</v>
+        <v>890.05</v>
       </c>
       <c r="G51">
         <v>385.3</v>
@@ -5469,28 +5469,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M51">
-        <v>55.9111609</v>
+        <v>57.052205</v>
       </c>
       <c r="N51">
-        <v>119.2623084877551</v>
+        <v>118.1212643877551</v>
       </c>
       <c r="O51">
-        <v>17.88934627316327</v>
+        <v>17.71818965816327</v>
       </c>
       <c r="P51">
-        <v>101.3729622145919</v>
+        <v>100.4030747295919</v>
       </c>
       <c r="Q51">
-        <v>359.8729622145918</v>
+        <v>358.9030747295918</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1875761799874311</v>
+        <v>0.1901775777853656</v>
       </c>
       <c r="T51">
-        <v>1.698442104006272</v>
+        <v>1.729606179309139</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.133068005886372</v>
+        <v>3.070406645768645</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1223312888926828</v>
+        <v>0.1223010759917758</v>
       </c>
       <c r="C52">
-        <v>1037.711700857724</v>
+        <v>1020.519871930377</v>
       </c>
       <c r="D52">
-        <v>1542.461700857724</v>
+        <v>1543.070871930377</v>
       </c>
       <c r="E52">
-        <v>197.9499999999999</v>
+        <v>215.751</v>
       </c>
       <c r="F52">
-        <v>890.05</v>
+        <v>907.851</v>
       </c>
       <c r="G52">
         <v>385.3</v>
@@ -5551,28 +5551,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M52">
-        <v>57.052205</v>
+        <v>58.1932491</v>
       </c>
       <c r="N52">
-        <v>118.1212643877551</v>
+        <v>116.9802202877551</v>
       </c>
       <c r="O52">
-        <v>17.71818965816327</v>
+        <v>17.54703304316327</v>
       </c>
       <c r="P52">
-        <v>100.4030747295919</v>
+        <v>99.43318724459185</v>
       </c>
       <c r="Q52">
-        <v>358.9030747295918</v>
+        <v>357.9331872445919</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1901775777853656</v>
+        <v>0.1928851550852567</v>
       </c>
       <c r="T52">
-        <v>1.729606179309139</v>
+        <v>1.762042257685593</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.070406645768645</v>
+        <v>3.010202593890828</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1223010759917758</v>
+        <v>0.1257184630908687</v>
       </c>
       <c r="C53">
-        <v>1020.519871930377</v>
+        <v>936.7357400384989</v>
       </c>
       <c r="D53">
-        <v>1543.070871930377</v>
+        <v>1477.087740038499</v>
       </c>
       <c r="E53">
-        <v>215.751</v>
+        <v>233.5519999999999</v>
       </c>
       <c r="F53">
-        <v>907.851</v>
+        <v>925.6519999999999</v>
       </c>
       <c r="G53">
         <v>385.3</v>
@@ -5633,45 +5633,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M53">
-        <v>58.1932491</v>
+        <v>66.55437879999999</v>
       </c>
       <c r="N53">
-        <v>116.9802202877551</v>
+        <v>108.6190905877551</v>
       </c>
       <c r="O53">
-        <v>17.54703304316327</v>
+        <v>16.29286358816327</v>
       </c>
       <c r="P53">
-        <v>99.43318724459185</v>
+        <v>92.32622699959185</v>
       </c>
       <c r="Q53">
-        <v>357.9331872445919</v>
+        <v>350.8262269995919</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1928851550852567</v>
+        <v>0.1957055481059765</v>
       </c>
       <c r="T53">
-        <v>1.762042257685593</v>
+        <v>1.795829839327733</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.010202593890828</v>
+        <v>2.632035225122635</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1257184630908687</v>
+        <v>0.1257545501899617</v>
       </c>
       <c r="C54">
-        <v>936.7357400384989</v>
+        <v>918.2680636390053</v>
       </c>
       <c r="D54">
-        <v>1477.087740038499</v>
+        <v>1476.421063639005</v>
       </c>
       <c r="E54">
-        <v>233.5519999999999</v>
+        <v>251.353</v>
       </c>
       <c r="F54">
-        <v>925.6519999999999</v>
+        <v>943.453</v>
       </c>
       <c r="G54">
         <v>385.3</v>
@@ -5715,28 +5715,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M54">
-        <v>66.55437879999999</v>
+        <v>67.8342707</v>
       </c>
       <c r="N54">
-        <v>108.6190905877551</v>
+        <v>107.3391986877551</v>
       </c>
       <c r="O54">
-        <v>16.29286358816327</v>
+        <v>16.10087980316327</v>
       </c>
       <c r="P54">
-        <v>92.32622699959185</v>
+        <v>91.23831888459185</v>
       </c>
       <c r="Q54">
-        <v>350.8262269995919</v>
+        <v>349.7383188845919</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1957055481059765</v>
+        <v>0.1986459578509823</v>
       </c>
       <c r="T54">
-        <v>1.795829839327733</v>
+        <v>1.831055190401452</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.632035225122635</v>
+        <v>2.582374183139189</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1257545501899617</v>
+        <v>0.1257906372890546</v>
       </c>
       <c r="C55">
-        <v>918.2680636390053</v>
+        <v>899.8009887703441</v>
       </c>
       <c r="D55">
-        <v>1476.421063639005</v>
+        <v>1475.754988770344</v>
       </c>
       <c r="E55">
-        <v>251.353</v>
+        <v>269.154</v>
       </c>
       <c r="F55">
-        <v>943.453</v>
+        <v>961.254</v>
       </c>
       <c r="G55">
         <v>385.3</v>
@@ -5797,28 +5797,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M55">
-        <v>67.8342707</v>
+        <v>69.1141626</v>
       </c>
       <c r="N55">
-        <v>107.3391986877551</v>
+        <v>106.0593067877551</v>
       </c>
       <c r="O55">
-        <v>16.10087980316327</v>
+        <v>15.90889601816327</v>
       </c>
       <c r="P55">
-        <v>91.23831888459185</v>
+        <v>90.15041076959186</v>
       </c>
       <c r="Q55">
-        <v>349.7383188845919</v>
+        <v>348.6504107695919</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1986459578509823</v>
+        <v>0.2017142114979448</v>
       </c>
       <c r="T55">
-        <v>1.831055190401452</v>
+        <v>1.867812078478377</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.582374183139189</v>
+        <v>2.534552439006982</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1257906372890546</v>
+        <v>0.1276499743881476</v>
       </c>
       <c r="C56">
-        <v>899.8009887703441</v>
+        <v>848.4761419969775</v>
       </c>
       <c r="D56">
-        <v>1475.754988770344</v>
+        <v>1442.231141996978</v>
       </c>
       <c r="E56">
-        <v>269.154</v>
+        <v>286.955</v>
       </c>
       <c r="F56">
-        <v>961.254</v>
+        <v>979.0550000000001</v>
       </c>
       <c r="G56">
         <v>385.3</v>
@@ -5879,45 +5879,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M56">
-        <v>69.1141626</v>
+        <v>74.21236900000001</v>
       </c>
       <c r="N56">
-        <v>106.0593067877551</v>
+        <v>100.9611003877551</v>
       </c>
       <c r="O56">
-        <v>15.90889601816327</v>
+        <v>15.14416505816327</v>
       </c>
       <c r="P56">
-        <v>90.15041076959186</v>
+        <v>85.81693532959184</v>
       </c>
       <c r="Q56">
-        <v>348.6504107695919</v>
+        <v>344.3169353295918</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2017142114979448</v>
+        <v>0.2049188319736613</v>
       </c>
       <c r="T56">
-        <v>1.867812078478377</v>
+        <v>1.906202606025388</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.15</v>
       </c>
       <c r="W56">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.534552439006982</v>
+        <v>2.360434948354163</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1276499743881476</v>
+        <v>0.1277192114872405</v>
       </c>
       <c r="C57">
-        <v>848.4761419969775</v>
+        <v>829.456186166221</v>
       </c>
       <c r="D57">
-        <v>1442.231141996978</v>
+        <v>1441.012186166221</v>
       </c>
       <c r="E57">
-        <v>286.955</v>
+        <v>304.756</v>
       </c>
       <c r="F57">
-        <v>979.0550000000001</v>
+        <v>996.856</v>
       </c>
       <c r="G57">
         <v>385.3</v>
@@ -5961,28 +5961,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M57">
-        <v>74.21236900000001</v>
+        <v>75.56168480000001</v>
       </c>
       <c r="N57">
-        <v>100.9611003877551</v>
+        <v>99.61178458775511</v>
       </c>
       <c r="O57">
-        <v>15.14416505816327</v>
+        <v>14.94176768816327</v>
       </c>
       <c r="P57">
-        <v>85.81693532959184</v>
+        <v>84.67001689959184</v>
       </c>
       <c r="Q57">
-        <v>344.3169353295918</v>
+        <v>343.1700168995918</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2049188319736613</v>
+        <v>0.2082691170164557</v>
       </c>
       <c r="T57">
-        <v>1.906202606025388</v>
+        <v>1.946338157551808</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.360434948354163</v>
+        <v>2.31828432427641</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1277192114872405</v>
+        <v>0.1277884485863335</v>
       </c>
       <c r="C58">
-        <v>829.456186166221</v>
+        <v>810.4382890880589</v>
       </c>
       <c r="D58">
-        <v>1441.012186166221</v>
+        <v>1439.795289088059</v>
       </c>
       <c r="E58">
-        <v>304.756</v>
+        <v>322.557</v>
       </c>
       <c r="F58">
-        <v>996.856</v>
+        <v>1014.657</v>
       </c>
       <c r="G58">
         <v>385.3</v>
@@ -6043,28 +6043,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M58">
-        <v>75.56168480000001</v>
+        <v>76.91100060000001</v>
       </c>
       <c r="N58">
-        <v>99.61178458775511</v>
+        <v>98.26246878775511</v>
       </c>
       <c r="O58">
-        <v>14.94176768816327</v>
+        <v>14.73937031816327</v>
       </c>
       <c r="P58">
-        <v>84.67001689959184</v>
+        <v>83.52309846959184</v>
       </c>
       <c r="Q58">
-        <v>343.1700168995918</v>
+        <v>342.0230984695918</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2082691170164557</v>
+        <v>0.2117752292705429</v>
       </c>
       <c r="T58">
-        <v>1.946338157551808</v>
+        <v>1.988340478916666</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.31828432427641</v>
+        <v>2.277612669464543</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1277884485863335</v>
+        <v>0.1278576856854264</v>
       </c>
       <c r="C59">
-        <v>810.4382890880589</v>
+        <v>791.4224455512051</v>
       </c>
       <c r="D59">
-        <v>1439.795289088059</v>
+        <v>1438.580445551205</v>
       </c>
       <c r="E59">
-        <v>322.557</v>
+        <v>340.3580000000001</v>
       </c>
       <c r="F59">
-        <v>1014.657</v>
+        <v>1032.458</v>
       </c>
       <c r="G59">
         <v>385.3</v>
@@ -6125,28 +6125,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M59">
-        <v>76.91100060000001</v>
+        <v>78.26031640000001</v>
       </c>
       <c r="N59">
-        <v>98.26246878775511</v>
+        <v>96.91315298775511</v>
       </c>
       <c r="O59">
-        <v>14.73937031816327</v>
+        <v>14.53697294816327</v>
       </c>
       <c r="P59">
-        <v>83.52309846959184</v>
+        <v>82.37618003959184</v>
       </c>
       <c r="Q59">
-        <v>342.0230984695918</v>
+        <v>340.8761800395919</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2117752292705429</v>
+        <v>0.2154482992510152</v>
       </c>
       <c r="T59">
-        <v>1.988340478916666</v>
+        <v>2.032342910822708</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.277612669464543</v>
+        <v>2.238343485508258</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1278576856854264</v>
+        <v>0.1279269227845193</v>
       </c>
       <c r="C60">
-        <v>791.4224455512053</v>
+        <v>772.4086503619449</v>
       </c>
       <c r="D60">
-        <v>1438.580445551205</v>
+        <v>1437.367650361945</v>
       </c>
       <c r="E60">
-        <v>340.3579999999998</v>
+        <v>358.1589999999998</v>
       </c>
       <c r="F60">
-        <v>1032.458</v>
+        <v>1050.259</v>
       </c>
       <c r="G60">
         <v>385.3</v>
@@ -6207,28 +6207,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M60">
-        <v>78.26031639999999</v>
+        <v>79.60963219999999</v>
       </c>
       <c r="N60">
-        <v>96.91315298775513</v>
+        <v>95.56383718775513</v>
       </c>
       <c r="O60">
-        <v>14.53697294816327</v>
+        <v>14.33457557816327</v>
       </c>
       <c r="P60">
-        <v>82.37618003959186</v>
+        <v>81.22926160959186</v>
       </c>
       <c r="Q60">
-        <v>340.8761800395919</v>
+        <v>339.7292616095918</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2154482992510152</v>
+        <v>0.2193005433768764</v>
       </c>
       <c r="T60">
-        <v>2.032342910822708</v>
+        <v>2.078491802821727</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.238343485508259</v>
+        <v>2.200405460330153</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1279269227845193</v>
+        <v>0.1279961598836123</v>
       </c>
       <c r="C61">
-        <v>772.4086503619449</v>
+        <v>753.3968983440648</v>
       </c>
       <c r="D61">
-        <v>1437.367650361945</v>
+        <v>1436.156898344065</v>
       </c>
       <c r="E61">
-        <v>358.1589999999998</v>
+        <v>375.9599999999999</v>
       </c>
       <c r="F61">
-        <v>1050.259</v>
+        <v>1068.06</v>
       </c>
       <c r="G61">
         <v>385.3</v>
@@ -6289,28 +6289,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M61">
-        <v>79.60963219999999</v>
+        <v>80.95894800000001</v>
       </c>
       <c r="N61">
-        <v>95.56383718775513</v>
+        <v>94.21452138775511</v>
       </c>
       <c r="O61">
-        <v>14.33457557816327</v>
+        <v>14.13217820816327</v>
       </c>
       <c r="P61">
-        <v>81.22926160959186</v>
+        <v>80.08234317959185</v>
       </c>
       <c r="Q61">
-        <v>339.7292616095918</v>
+        <v>338.5823431795918</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2193005433768764</v>
+        <v>0.2233453997090307</v>
       </c>
       <c r="T61">
-        <v>2.078491802821727</v>
+        <v>2.126948139420698</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.200405460330153</v>
+        <v>2.163732035991316</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1279961598836123</v>
+        <v>0.1280653969827052</v>
       </c>
       <c r="C62">
-        <v>753.3968983440648</v>
+        <v>734.3871843387751</v>
       </c>
       <c r="D62">
-        <v>1436.156898344065</v>
+        <v>1434.948184338775</v>
       </c>
       <c r="E62">
-        <v>375.9599999999999</v>
+        <v>393.7609999999999</v>
       </c>
       <c r="F62">
-        <v>1068.06</v>
+        <v>1085.861</v>
       </c>
       <c r="G62">
         <v>385.3</v>
@@ -6371,28 +6371,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M62">
-        <v>80.95894800000001</v>
+        <v>82.30826379999999</v>
       </c>
       <c r="N62">
-        <v>94.21452138775511</v>
+        <v>92.86520558775513</v>
       </c>
       <c r="O62">
-        <v>14.13217820816327</v>
+        <v>13.92978083816327</v>
       </c>
       <c r="P62">
-        <v>80.08234317959185</v>
+        <v>78.93542474959186</v>
       </c>
       <c r="Q62">
-        <v>338.5823431795918</v>
+        <v>337.4354247495918</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2233453997090307</v>
+        <v>0.227597684571039</v>
       </c>
       <c r="T62">
-        <v>2.126948139420698</v>
+        <v>2.177889416358077</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.163732035991316</v>
+        <v>2.128261019007852</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1280653969827052</v>
+        <v>0.1281346340817982</v>
       </c>
       <c r="C63">
-        <v>734.3871843387751</v>
+        <v>715.3795032046414</v>
       </c>
       <c r="D63">
-        <v>1434.948184338775</v>
+        <v>1433.741503204642</v>
       </c>
       <c r="E63">
-        <v>393.7609999999999</v>
+        <v>411.562</v>
       </c>
       <c r="F63">
-        <v>1085.861</v>
+        <v>1103.662</v>
       </c>
       <c r="G63">
         <v>385.3</v>
@@ -6453,28 +6453,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M63">
-        <v>82.30826379999999</v>
+        <v>83.65757960000001</v>
       </c>
       <c r="N63">
-        <v>92.86520558775513</v>
+        <v>91.51588978775511</v>
       </c>
       <c r="O63">
-        <v>13.92978083816327</v>
+        <v>13.72738346816327</v>
       </c>
       <c r="P63">
-        <v>78.93542474959186</v>
+        <v>77.78850631959185</v>
       </c>
       <c r="Q63">
-        <v>337.4354247495918</v>
+        <v>336.2885063195919</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.227597684571039</v>
+        <v>0.2320737738994689</v>
       </c>
       <c r="T63">
-        <v>2.177889416358077</v>
+        <v>2.231511813134266</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.128261019007852</v>
+        <v>2.093934228378693</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1281346340817982</v>
+        <v>0.1282038711808911</v>
       </c>
       <c r="C64">
-        <v>715.3795032046414</v>
+        <v>696.3738498175073</v>
       </c>
       <c r="D64">
-        <v>1433.741503204642</v>
+        <v>1432.536849817507</v>
       </c>
       <c r="E64">
-        <v>411.562</v>
+        <v>429.3629999999999</v>
       </c>
       <c r="F64">
-        <v>1103.662</v>
+        <v>1121.463</v>
       </c>
       <c r="G64">
         <v>385.3</v>
@@ -6535,28 +6535,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M64">
-        <v>83.65757960000001</v>
+        <v>85.0068954</v>
       </c>
       <c r="N64">
-        <v>91.51588978775511</v>
+        <v>90.16657398775511</v>
       </c>
       <c r="O64">
-        <v>13.72738346816327</v>
+        <v>13.52498609816327</v>
       </c>
       <c r="P64">
-        <v>77.78850631959185</v>
+        <v>76.64158788959185</v>
       </c>
       <c r="Q64">
-        <v>336.2885063195919</v>
+        <v>335.1415878895918</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2320737738994689</v>
+        <v>0.2367918140024085</v>
       </c>
       <c r="T64">
-        <v>2.231511813134266</v>
+        <v>2.288032717844303</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.093934228378693</v>
+        <v>2.060697177134587</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1282038711808911</v>
+        <v>0.1282731082799841</v>
       </c>
       <c r="C65">
-        <v>696.3738498175073</v>
+        <v>677.3702190704232</v>
       </c>
       <c r="D65">
-        <v>1432.536849817507</v>
+        <v>1431.334219070423</v>
       </c>
       <c r="E65">
-        <v>429.3629999999999</v>
+        <v>447.1639999999999</v>
       </c>
       <c r="F65">
-        <v>1121.463</v>
+        <v>1139.264</v>
       </c>
       <c r="G65">
         <v>385.3</v>
@@ -6617,28 +6617,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M65">
-        <v>85.0068954</v>
+        <v>86.3562112</v>
       </c>
       <c r="N65">
-        <v>90.16657398775511</v>
+        <v>88.81725818775512</v>
       </c>
       <c r="O65">
-        <v>13.52498609816327</v>
+        <v>13.32258872816327</v>
       </c>
       <c r="P65">
-        <v>76.64158788959185</v>
+        <v>75.49466945959185</v>
       </c>
       <c r="Q65">
-        <v>335.1415878895918</v>
+        <v>333.9946694595918</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2367918140024085</v>
+        <v>0.2417719674444002</v>
       </c>
       <c r="T65">
-        <v>2.288032717844303</v>
+        <v>2.347693672816009</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.060697177134587</v>
+        <v>2.028498783741859</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1282731082799841</v>
+        <v>0.136187845379077</v>
       </c>
       <c r="C66">
-        <v>677.3702190704232</v>
+        <v>534.235619211207</v>
       </c>
       <c r="D66">
-        <v>1431.334219070423</v>
+        <v>1306.000619211207</v>
       </c>
       <c r="E66">
-        <v>447.1639999999999</v>
+        <v>464.965</v>
       </c>
       <c r="F66">
-        <v>1139.264</v>
+        <v>1157.065</v>
       </c>
       <c r="G66">
         <v>385.3</v>
@@ -6699,45 +6699,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M66">
-        <v>86.3562112</v>
+        <v>104.13585</v>
       </c>
       <c r="N66">
-        <v>88.81725818775512</v>
+        <v>71.03761938775511</v>
       </c>
       <c r="O66">
-        <v>13.32258872816327</v>
+        <v>10.65564290816327</v>
       </c>
       <c r="P66">
-        <v>75.49466945959185</v>
+        <v>60.38197647959185</v>
       </c>
       <c r="Q66">
-        <v>333.9946694595918</v>
+        <v>318.8819764795919</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2417719674444002</v>
+        <v>0.2470367010830772</v>
       </c>
       <c r="T66">
-        <v>2.347693672816009</v>
+        <v>2.410763825214669</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.15</v>
       </c>
       <c r="W66">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.028498783741859</v>
+        <v>1.682162957211711</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.136187845379077</v>
+        <v>0.13637778247817</v>
       </c>
       <c r="C67">
-        <v>534.235619211207</v>
+        <v>513.696000951411</v>
       </c>
       <c r="D67">
-        <v>1306.000619211207</v>
+        <v>1303.262000951411</v>
       </c>
       <c r="E67">
-        <v>464.965</v>
+        <v>482.766</v>
       </c>
       <c r="F67">
-        <v>1157.065</v>
+        <v>1174.866</v>
       </c>
       <c r="G67">
         <v>385.3</v>
@@ -6781,28 +6781,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M67">
-        <v>104.13585</v>
+        <v>105.73794</v>
       </c>
       <c r="N67">
-        <v>71.03761938775511</v>
+        <v>69.43552938775512</v>
       </c>
       <c r="O67">
-        <v>10.65564290816327</v>
+        <v>10.41532940816327</v>
       </c>
       <c r="P67">
-        <v>60.38197647959185</v>
+        <v>59.02019997959186</v>
       </c>
       <c r="Q67">
-        <v>318.8819764795919</v>
+        <v>317.5201999795918</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2470367010830772</v>
+        <v>0.252611124935794</v>
       </c>
       <c r="T67">
-        <v>2.410763825214669</v>
+        <v>2.477543986577956</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.682162957211711</v>
+        <v>1.6566756396782</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.13637778247817</v>
+        <v>0.1365677195772629</v>
       </c>
       <c r="C68">
-        <v>513.696000951411</v>
+        <v>493.1678441497236</v>
       </c>
       <c r="D68">
-        <v>1303.262000951411</v>
+        <v>1300.534844149724</v>
       </c>
       <c r="E68">
-        <v>482.766</v>
+        <v>500.5669999999999</v>
       </c>
       <c r="F68">
-        <v>1174.866</v>
+        <v>1192.667</v>
       </c>
       <c r="G68">
         <v>385.3</v>
@@ -6863,28 +6863,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M68">
-        <v>105.73794</v>
+        <v>107.34003</v>
       </c>
       <c r="N68">
-        <v>69.43552938775512</v>
+        <v>67.83343938775513</v>
       </c>
       <c r="O68">
-        <v>10.41532940816327</v>
+        <v>10.17501590816327</v>
       </c>
       <c r="P68">
-        <v>59.02019997959186</v>
+        <v>57.65842347959187</v>
       </c>
       <c r="Q68">
-        <v>317.5201999795918</v>
+        <v>316.1584234795919</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.252611124935794</v>
+        <v>0.2585233926583725</v>
       </c>
       <c r="T68">
-        <v>2.477543986577956</v>
+        <v>2.54837143044811</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.6566756396782</v>
+        <v>1.631949137593451</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1365677195772629</v>
+        <v>0.1367576566763559</v>
       </c>
       <c r="C69">
-        <v>493.1678441497236</v>
+        <v>472.6510770049513</v>
       </c>
       <c r="D69">
-        <v>1300.534844149724</v>
+        <v>1297.819077004951</v>
       </c>
       <c r="E69">
-        <v>500.5669999999999</v>
+        <v>518.3680000000001</v>
       </c>
       <c r="F69">
-        <v>1192.667</v>
+        <v>1210.468</v>
       </c>
       <c r="G69">
         <v>385.3</v>
@@ -6945,28 +6945,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M69">
-        <v>107.34003</v>
+        <v>108.94212</v>
       </c>
       <c r="N69">
-        <v>67.83343938775513</v>
+        <v>66.23134938775512</v>
       </c>
       <c r="O69">
-        <v>10.17501590816327</v>
+        <v>9.934702408163266</v>
       </c>
       <c r="P69">
-        <v>57.65842347959187</v>
+        <v>56.29664697959185</v>
       </c>
       <c r="Q69">
-        <v>316.1584234795919</v>
+        <v>314.7966469795919</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2585233926583725</v>
+        <v>0.2648051771136121</v>
       </c>
       <c r="T69">
-        <v>2.54837143044811</v>
+        <v>2.623625589560147</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.631949137593451</v>
+        <v>1.607949885570017</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1367576566763559</v>
+        <v>0.1369475937754488</v>
       </c>
       <c r="C70">
-        <v>472.6510770049513</v>
+        <v>452.1456283143905</v>
       </c>
       <c r="D70">
-        <v>1297.819077004951</v>
+        <v>1295.114628314391</v>
       </c>
       <c r="E70">
-        <v>518.3680000000001</v>
+        <v>536.169</v>
       </c>
       <c r="F70">
-        <v>1210.468</v>
+        <v>1228.269</v>
       </c>
       <c r="G70">
         <v>385.3</v>
@@ -7027,28 +7027,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M70">
-        <v>108.94212</v>
+        <v>110.54421</v>
       </c>
       <c r="N70">
-        <v>66.23134938775512</v>
+        <v>64.62925938775513</v>
       </c>
       <c r="O70">
-        <v>9.934702408163266</v>
+        <v>9.694388908163269</v>
       </c>
       <c r="P70">
-        <v>56.29664697959185</v>
+        <v>54.93487047959186</v>
       </c>
       <c r="Q70">
-        <v>314.7966469795919</v>
+        <v>313.4348704795918</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2648051771136121</v>
+        <v>0.2714922379853187</v>
       </c>
       <c r="T70">
-        <v>2.623625589560147</v>
+        <v>2.703734855711672</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.607949885570017</v>
+        <v>1.584646264040017</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1369475937754488</v>
+        <v>0.1371375308745418</v>
       </c>
       <c r="C71">
-        <v>452.1456283143905</v>
+        <v>431.6514274676019</v>
       </c>
       <c r="D71">
-        <v>1295.114628314391</v>
+        <v>1292.421427467602</v>
       </c>
       <c r="E71">
-        <v>536.169</v>
+        <v>553.9700000000001</v>
       </c>
       <c r="F71">
-        <v>1228.269</v>
+        <v>1246.07</v>
       </c>
       <c r="G71">
         <v>385.3</v>
@@ -7109,28 +7109,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M71">
-        <v>110.54421</v>
+        <v>112.1463</v>
       </c>
       <c r="N71">
-        <v>64.62925938775513</v>
+        <v>63.02716938775511</v>
       </c>
       <c r="O71">
-        <v>9.694388908163269</v>
+        <v>9.454075408163266</v>
       </c>
       <c r="P71">
-        <v>54.93487047959186</v>
+        <v>53.57309397959185</v>
       </c>
       <c r="Q71">
-        <v>313.4348704795918</v>
+        <v>312.0730939795918</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2714922379853187</v>
+        <v>0.2786251029151392</v>
       </c>
       <c r="T71">
-        <v>2.703734855711672</v>
+        <v>2.78918473960663</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.584646264040017</v>
+        <v>1.562008460268017</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1371375308745418</v>
+        <v>0.1373274679736347</v>
       </c>
       <c r="C72">
-        <v>431.6514274676019</v>
+        <v>411.1684044402689</v>
       </c>
       <c r="D72">
-        <v>1292.421427467602</v>
+        <v>1289.739404440269</v>
       </c>
       <c r="E72">
-        <v>553.9700000000001</v>
+        <v>571.7710000000001</v>
       </c>
       <c r="F72">
-        <v>1246.07</v>
+        <v>1263.871</v>
       </c>
       <c r="G72">
         <v>385.3</v>
@@ -7191,28 +7191,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M72">
-        <v>112.1463</v>
+        <v>113.74839</v>
       </c>
       <c r="N72">
-        <v>63.02716938775511</v>
+        <v>61.42507938775512</v>
       </c>
       <c r="O72">
-        <v>9.454075408163266</v>
+        <v>9.213761908163267</v>
       </c>
       <c r="P72">
-        <v>53.57309397959185</v>
+        <v>52.21131747959186</v>
       </c>
       <c r="Q72">
-        <v>312.0730939795918</v>
+        <v>310.7113174795919</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2786251029151392</v>
+        <v>0.2862498895642577</v>
       </c>
       <c r="T72">
-        <v>2.78918473960663</v>
+        <v>2.880527718942622</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.562008460268017</v>
+        <v>1.540008341109313</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1373274679736347</v>
+        <v>0.1375174050727276</v>
       </c>
       <c r="C73">
-        <v>411.1684044402691</v>
+        <v>390.6964897881269</v>
       </c>
       <c r="D73">
-        <v>1289.739404440269</v>
+        <v>1287.068489788127</v>
       </c>
       <c r="E73">
-        <v>571.7709999999998</v>
+        <v>589.5719999999998</v>
       </c>
       <c r="F73">
-        <v>1263.871</v>
+        <v>1281.672</v>
       </c>
       <c r="G73">
         <v>385.3</v>
@@ -7273,28 +7273,28 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M73">
-        <v>113.74839</v>
+        <v>115.35048</v>
       </c>
       <c r="N73">
-        <v>61.42507938775513</v>
+        <v>59.82298938775514</v>
       </c>
       <c r="O73">
-        <v>9.213761908163269</v>
+        <v>8.973448408163271</v>
       </c>
       <c r="P73">
-        <v>52.21131747959186</v>
+        <v>50.84954097959187</v>
       </c>
       <c r="Q73">
-        <v>310.7113174795919</v>
+        <v>309.3495409795919</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2862498895642576</v>
+        <v>0.2944193038311701</v>
       </c>
       <c r="T73">
-        <v>2.88052771894262</v>
+        <v>2.97839519680261</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.540008341109313</v>
+        <v>1.518619336371684</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1375174050727276</v>
+        <v>0.1749637099688699</v>
       </c>
       <c r="C74">
-        <v>390.6964897881269</v>
+        <v>-0.2430574279558186</v>
       </c>
       <c r="D74">
-        <v>1287.068489788127</v>
+        <v>913.9299425720441</v>
       </c>
       <c r="E74">
-        <v>589.5719999999998</v>
+        <v>607.3729999999999</v>
       </c>
       <c r="F74">
-        <v>1281.672</v>
+        <v>1299.473</v>
       </c>
       <c r="G74">
         <v>385.3</v>
@@ -7355,45 +7355,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M74">
-        <v>115.35048</v>
+        <v>190.7626364</v>
       </c>
       <c r="N74">
-        <v>59.82298938775514</v>
+        <v>-15.5891670122449</v>
       </c>
       <c r="O74">
-        <v>8.973448408163271</v>
+        <v>-2.338375051836735</v>
       </c>
       <c r="P74">
-        <v>50.84954097959187</v>
+        <v>-13.25079196040816</v>
       </c>
       <c r="Q74">
-        <v>309.3495409795919</v>
+        <v>245.2492080395918</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2944193038311701</v>
+        <v>0.3057803330311208</v>
       </c>
       <c r="T74">
-        <v>2.97839519680261</v>
+        <v>3.114497399159533</v>
       </c>
       <c r="U74">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.15</v>
+        <v>0.1377419651145232</v>
       </c>
       <c r="W74">
-        <v>0.0765</v>
+        <v>0.126579479521188</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.518619336371684</v>
+        <v>0.9182797674301544</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1749637099688699</v>
+        <v>0.1759737099688699</v>
       </c>
       <c r="C75">
-        <v>-0.2430574279558186</v>
+        <v>-25.13511477139718</v>
       </c>
       <c r="D75">
-        <v>913.9299425720441</v>
+        <v>906.8388852286026</v>
       </c>
       <c r="E75">
-        <v>607.3729999999999</v>
+        <v>625.1739999999999</v>
       </c>
       <c r="F75">
-        <v>1299.473</v>
+        <v>1317.274</v>
       </c>
       <c r="G75">
         <v>385.3</v>
@@ -7437,37 +7437,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M75">
-        <v>190.7626364</v>
+        <v>193.3758232</v>
       </c>
       <c r="N75">
-        <v>-15.5891670122449</v>
+        <v>-18.20235381224489</v>
       </c>
       <c r="O75">
-        <v>-2.338375051836735</v>
+        <v>-2.730353071836734</v>
       </c>
       <c r="P75">
-        <v>-13.25079196040816</v>
+        <v>-15.47200074040816</v>
       </c>
       <c r="Q75">
-        <v>245.2492080395918</v>
+        <v>243.0279992595918</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3057803330311208</v>
+        <v>0.3157795766092409</v>
       </c>
       <c r="T75">
-        <v>3.114497399159533</v>
+        <v>3.23428576066567</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1377419651145232</v>
+        <v>0.1358805872075701</v>
       </c>
       <c r="W75">
-        <v>0.126579479521188</v>
+        <v>0.1268527297979287</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9182797674301544</v>
+        <v>0.9058705813838009</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1759737099688699</v>
+        <v>0.1769837099688699</v>
       </c>
       <c r="C76">
-        <v>-25.13511477139718</v>
+        <v>-49.91798221742556</v>
       </c>
       <c r="D76">
-        <v>906.8388852286026</v>
+        <v>899.8570177825743</v>
       </c>
       <c r="E76">
-        <v>625.1739999999999</v>
+        <v>642.9749999999998</v>
       </c>
       <c r="F76">
-        <v>1317.274</v>
+        <v>1335.075</v>
       </c>
       <c r="G76">
         <v>385.3</v>
@@ -7519,37 +7519,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M76">
-        <v>193.3758232</v>
+        <v>195.98901</v>
       </c>
       <c r="N76">
-        <v>-18.20235381224489</v>
+        <v>-20.81554061224486</v>
       </c>
       <c r="O76">
-        <v>-2.730353071836734</v>
+        <v>-3.122331091836729</v>
       </c>
       <c r="P76">
-        <v>-15.47200074040816</v>
+        <v>-17.69320952040813</v>
       </c>
       <c r="Q76">
-        <v>243.0279992595918</v>
+        <v>240.8067904795919</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3157795766092409</v>
+        <v>0.3265787596736105</v>
       </c>
       <c r="T76">
-        <v>3.23428576066567</v>
+        <v>3.363657191092297</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1358805872075701</v>
+        <v>0.1340688460448025</v>
       </c>
       <c r="W76">
-        <v>0.1268527297979287</v>
+        <v>0.127118693400623</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9058705813838009</v>
+        <v>0.8937923069653504</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1769837099688699</v>
+        <v>0.1779937099688699</v>
       </c>
       <c r="C77">
-        <v>-49.91798221742556</v>
+        <v>-74.59416249774608</v>
       </c>
       <c r="D77">
-        <v>899.8570177825743</v>
+        <v>892.9818375022538</v>
       </c>
       <c r="E77">
-        <v>642.9749999999998</v>
+        <v>660.776</v>
       </c>
       <c r="F77">
-        <v>1335.075</v>
+        <v>1352.876</v>
       </c>
       <c r="G77">
         <v>385.3</v>
@@ -7601,37 +7601,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M77">
-        <v>195.98901</v>
+        <v>198.6021968</v>
       </c>
       <c r="N77">
-        <v>-20.81554061224486</v>
+        <v>-23.42872741224488</v>
       </c>
       <c r="O77">
-        <v>-3.122331091836729</v>
+        <v>-3.514309111836732</v>
       </c>
       <c r="P77">
-        <v>-17.69320952040813</v>
+        <v>-19.91441830040815</v>
       </c>
       <c r="Q77">
-        <v>240.8067904795919</v>
+        <v>238.5855816995918</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3265787596736105</v>
+        <v>0.338277874660011</v>
       </c>
       <c r="T77">
-        <v>3.363657191092297</v>
+        <v>3.503809574054476</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1340688460448025</v>
+        <v>0.1323047822810551</v>
       </c>
       <c r="W77">
-        <v>0.127118693400623</v>
+        <v>0.1273776579611411</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8937923069653504</v>
+        <v>0.882031881873701</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1779937099688699</v>
+        <v>0.1790037099688699</v>
       </c>
       <c r="C78">
-        <v>-74.59416249774608</v>
+        <v>-99.16608243749897</v>
       </c>
       <c r="D78">
-        <v>892.9818375022538</v>
+        <v>886.210917562501</v>
       </c>
       <c r="E78">
-        <v>660.776</v>
+        <v>678.5769999999999</v>
       </c>
       <c r="F78">
-        <v>1352.876</v>
+        <v>1370.677</v>
       </c>
       <c r="G78">
         <v>385.3</v>
@@ -7683,37 +7683,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M78">
-        <v>198.6021968</v>
+        <v>201.2153836</v>
       </c>
       <c r="N78">
-        <v>-23.42872741224488</v>
+        <v>-26.04191421224488</v>
       </c>
       <c r="O78">
-        <v>-3.514309111836732</v>
+        <v>-3.906287131836731</v>
       </c>
       <c r="P78">
-        <v>-19.91441830040815</v>
+        <v>-22.13562708040815</v>
       </c>
       <c r="Q78">
-        <v>238.5855816995918</v>
+        <v>236.3643729195919</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.338277874660011</v>
+        <v>0.3509943039930549</v>
       </c>
       <c r="T78">
-        <v>3.503809574054476</v>
+        <v>3.656149120752496</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1323047822810551</v>
+        <v>0.1305865383553272</v>
       </c>
       <c r="W78">
-        <v>0.1273776579611411</v>
+        <v>0.127629896169438</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.882031881873701</v>
+        <v>0.8705769223688478</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1790037099688699</v>
+        <v>0.1800137099688699</v>
       </c>
       <c r="C79">
-        <v>-99.16608243749897</v>
+        <v>-123.6360958113619</v>
       </c>
       <c r="D79">
-        <v>886.210917562501</v>
+        <v>879.5419041886381</v>
       </c>
       <c r="E79">
-        <v>678.5769999999999</v>
+        <v>696.378</v>
       </c>
       <c r="F79">
-        <v>1370.677</v>
+        <v>1388.478</v>
       </c>
       <c r="G79">
         <v>385.3</v>
@@ -7765,37 +7765,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M79">
-        <v>201.2153836</v>
+        <v>203.8285704</v>
       </c>
       <c r="N79">
-        <v>-26.04191421224488</v>
+        <v>-28.6551010122449</v>
       </c>
       <c r="O79">
-        <v>-3.906287131836731</v>
+        <v>-4.298265151836735</v>
       </c>
       <c r="P79">
-        <v>-22.13562708040815</v>
+        <v>-24.35683586040816</v>
       </c>
       <c r="Q79">
-        <v>236.3643729195919</v>
+        <v>234.1431641395918</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3509943039930549</v>
+        <v>0.3648667723563756</v>
       </c>
       <c r="T79">
-        <v>3.656149120752496</v>
+        <v>3.822337717150337</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1305865383553272</v>
+        <v>0.1289123519661563</v>
       </c>
       <c r="W79">
-        <v>0.127629896169438</v>
+        <v>0.1278756667313683</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8705769223688478</v>
+        <v>0.8594156797743753</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1800137099688699</v>
+        <v>0.1810237099688699</v>
       </c>
       <c r="C80">
-        <v>-123.6360958113619</v>
+        <v>-148.0064860716575</v>
       </c>
       <c r="D80">
-        <v>879.5419041886381</v>
+        <v>872.9725139283424</v>
       </c>
       <c r="E80">
-        <v>696.378</v>
+        <v>714.179</v>
       </c>
       <c r="F80">
-        <v>1388.478</v>
+        <v>1406.279</v>
       </c>
       <c r="G80">
         <v>385.3</v>
@@ -7847,37 +7847,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M80">
-        <v>203.8285704</v>
+        <v>206.4417572</v>
       </c>
       <c r="N80">
-        <v>-28.6551010122449</v>
+        <v>-31.26828781224489</v>
       </c>
       <c r="O80">
-        <v>-4.298265151836735</v>
+        <v>-4.690243171836734</v>
       </c>
       <c r="P80">
-        <v>-24.35683586040816</v>
+        <v>-26.57804464040816</v>
       </c>
       <c r="Q80">
-        <v>234.1431641395918</v>
+        <v>231.9219553595918</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3648667723563756</v>
+        <v>0.3800604281828698</v>
       </c>
       <c r="T80">
-        <v>3.822337717150337</v>
+        <v>4.004353798919402</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1289123519661563</v>
+        <v>0.1272805500425341</v>
       </c>
       <c r="W80">
-        <v>0.1278756667313683</v>
+        <v>0.128115215253756</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8594156797743753</v>
+        <v>0.8485370002835604</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1810237099688699</v>
+        <v>0.1820337099688699</v>
       </c>
       <c r="C81">
-        <v>-148.0064860716575</v>
+        <v>-172.2794689551088</v>
       </c>
       <c r="D81">
-        <v>872.9725139283424</v>
+        <v>866.5005310448911</v>
       </c>
       <c r="E81">
-        <v>714.179</v>
+        <v>731.9799999999999</v>
       </c>
       <c r="F81">
-        <v>1406.279</v>
+        <v>1424.08</v>
       </c>
       <c r="G81">
         <v>385.3</v>
@@ -7929,37 +7929,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M81">
-        <v>206.4417572</v>
+        <v>209.054944</v>
       </c>
       <c r="N81">
-        <v>-31.26828781224489</v>
+        <v>-33.88147461224489</v>
       </c>
       <c r="O81">
-        <v>-4.690243171836734</v>
+        <v>-5.082221191836733</v>
       </c>
       <c r="P81">
-        <v>-26.57804464040816</v>
+        <v>-28.79925342040815</v>
       </c>
       <c r="Q81">
-        <v>231.9219553595918</v>
+        <v>229.7007465795919</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3800604281828698</v>
+        <v>0.3967734495920133</v>
       </c>
       <c r="T81">
-        <v>4.004353798919402</v>
+        <v>4.204571488865372</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1272805500425341</v>
+        <v>0.1256895431670024</v>
       </c>
       <c r="W81">
-        <v>0.128115215253756</v>
+        <v>0.1283487750630841</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8485370002835604</v>
+        <v>0.8379302877800159</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1820337099688699</v>
+        <v>0.1830437099688699</v>
       </c>
       <c r="C82">
-        <v>-172.2794689551088</v>
+        <v>-196.4571949744934</v>
       </c>
       <c r="D82">
-        <v>866.5005310448911</v>
+        <v>860.1238050255067</v>
       </c>
       <c r="E82">
-        <v>731.9799999999999</v>
+        <v>749.7810000000001</v>
       </c>
       <c r="F82">
-        <v>1424.08</v>
+        <v>1441.881</v>
       </c>
       <c r="G82">
         <v>385.3</v>
@@ -8011,37 +8011,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M82">
-        <v>209.054944</v>
+        <v>211.6681308</v>
       </c>
       <c r="N82">
-        <v>-33.88147461224489</v>
+        <v>-36.49466141224491</v>
       </c>
       <c r="O82">
-        <v>-5.082221191836733</v>
+        <v>-5.474199211836736</v>
       </c>
       <c r="P82">
-        <v>-28.79925342040815</v>
+        <v>-31.02046220040817</v>
       </c>
       <c r="Q82">
-        <v>229.7007465795919</v>
+        <v>227.4795377995918</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3967734495920133</v>
+        <v>0.4152457364126455</v>
       </c>
       <c r="T82">
-        <v>4.204571488865372</v>
+        <v>4.425864725121444</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1256895431670024</v>
+        <v>0.1241378204118542</v>
       </c>
       <c r="W82">
-        <v>0.1283487750630841</v>
+        <v>0.1285765679635398</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8379302877800159</v>
+        <v>0.8275854694123613</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1830437099688699</v>
+        <v>0.1840537099688699</v>
       </c>
       <c r="C83">
-        <v>-196.4571949744934</v>
+        <v>-220.5417518010795</v>
       </c>
       <c r="D83">
-        <v>860.1238050255067</v>
+        <v>853.8402481989206</v>
       </c>
       <c r="E83">
-        <v>749.7810000000001</v>
+        <v>767.582</v>
       </c>
       <c r="F83">
-        <v>1441.881</v>
+        <v>1459.682</v>
       </c>
       <c r="G83">
         <v>385.3</v>
@@ -8093,37 +8093,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M83">
-        <v>211.6681308</v>
+        <v>214.2813176</v>
       </c>
       <c r="N83">
-        <v>-36.49466141224491</v>
+        <v>-39.1078482122449</v>
       </c>
       <c r="O83">
-        <v>-5.474199211836736</v>
+        <v>-5.866177231836735</v>
       </c>
       <c r="P83">
-        <v>-31.02046220040817</v>
+        <v>-33.24167098040817</v>
       </c>
       <c r="Q83">
-        <v>227.4795377995918</v>
+        <v>225.2583290195918</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4152457364126455</v>
+        <v>0.4357704995466813</v>
       </c>
       <c r="T83">
-        <v>4.425864725121444</v>
+        <v>4.671746098739302</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1241378204118542</v>
+        <v>0.122623944553173</v>
       </c>
       <c r="W83">
-        <v>0.1285765679635398</v>
+        <v>0.1287988049395942</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8275854694123613</v>
+        <v>0.8174929636878203</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1840537099688699</v>
+        <v>0.1850637099688699</v>
       </c>
       <c r="C84">
-        <v>-220.5417518010795</v>
+        <v>-244.5351665433959</v>
       </c>
       <c r="D84">
-        <v>853.8402481989206</v>
+        <v>847.647833456604</v>
       </c>
       <c r="E84">
-        <v>767.582</v>
+        <v>785.3829999999999</v>
       </c>
       <c r="F84">
-        <v>1459.682</v>
+        <v>1477.483</v>
       </c>
       <c r="G84">
         <v>385.3</v>
@@ -8175,37 +8175,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M84">
-        <v>214.2813176</v>
+        <v>216.8945044</v>
       </c>
       <c r="N84">
-        <v>-39.1078482122449</v>
+        <v>-41.7210350122449</v>
       </c>
       <c r="O84">
-        <v>-5.866177231836735</v>
+        <v>-6.258155251836734</v>
       </c>
       <c r="P84">
-        <v>-33.24167098040817</v>
+        <v>-35.46287976040816</v>
       </c>
       <c r="Q84">
-        <v>225.2583290195918</v>
+        <v>223.0371202395918</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4357704995466813</v>
+        <v>0.4587099406964862</v>
       </c>
       <c r="T84">
-        <v>4.671746098739302</v>
+        <v>4.946554692782791</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.122623944553173</v>
+        <v>0.1211465476308457</v>
       </c>
       <c r="W84">
-        <v>0.1287988049395942</v>
+        <v>0.1290156868077919</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8174929636878203</v>
+        <v>0.8076436508723045</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1850637099688699</v>
+        <v>0.2335440245956636</v>
       </c>
       <c r="C85">
-        <v>-244.5351665433959</v>
+        <v>-481.2205424759943</v>
       </c>
       <c r="D85">
-        <v>847.647833456604</v>
+        <v>628.7634575240058</v>
       </c>
       <c r="E85">
-        <v>785.3829999999999</v>
+        <v>803.1840000000001</v>
       </c>
       <c r="F85">
-        <v>1477.483</v>
+        <v>1495.284</v>
       </c>
       <c r="G85">
         <v>385.3</v>
@@ -8257,45 +8257,45 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M85">
-        <v>216.8945044</v>
+        <v>300.2530272</v>
       </c>
       <c r="N85">
-        <v>-41.7210350122449</v>
+        <v>-125.0795578122449</v>
       </c>
       <c r="O85">
-        <v>-6.258155251836734</v>
+        <v>-18.76193367183673</v>
       </c>
       <c r="P85">
-        <v>-35.46287976040816</v>
+        <v>-106.3176241404082</v>
       </c>
       <c r="Q85">
-        <v>223.0371202395918</v>
+        <v>152.1823758595918</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4587099406964862</v>
+        <v>0.4977062784074773</v>
       </c>
       <c r="T85">
-        <v>4.946554692782791</v>
+        <v>5.413720770160998</v>
       </c>
       <c r="U85">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1211465476308457</v>
+        <v>0.08751292419330274</v>
       </c>
       <c r="W85">
-        <v>0.1290156868077919</v>
+        <v>0.1832274048219848</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8076436508723045</v>
+        <v>0.5834194946220183</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2335440245956636</v>
+        <v>0.2350940245956636</v>
       </c>
       <c r="C86">
-        <v>-481.2205424759941</v>
+        <v>-504.1700587128055</v>
       </c>
       <c r="D86">
-        <v>628.7634575240058</v>
+        <v>623.6149412871943</v>
       </c>
       <c r="E86">
-        <v>803.1839999999999</v>
+        <v>820.9849999999998</v>
       </c>
       <c r="F86">
-        <v>1495.284</v>
+        <v>1513.085</v>
       </c>
       <c r="G86">
         <v>385.3</v>
@@ -8339,37 +8339,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M86">
-        <v>300.2530272</v>
+        <v>303.827468</v>
       </c>
       <c r="N86">
-        <v>-125.0795578122448</v>
+        <v>-128.6539986122448</v>
       </c>
       <c r="O86">
-        <v>-18.76193367183673</v>
+        <v>-19.29809979183672</v>
       </c>
       <c r="P86">
-        <v>-106.3176241404081</v>
+        <v>-109.3558988204081</v>
       </c>
       <c r="Q86">
-        <v>152.1823758595919</v>
+        <v>149.1441011795919</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.497706278407477</v>
+        <v>0.5278333636346421</v>
       </c>
       <c r="T86">
-        <v>5.413720770160994</v>
+        <v>5.774635488171727</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.08751292419330275</v>
+        <v>0.08648336037926389</v>
       </c>
       <c r="W86">
-        <v>0.1832274048219848</v>
+        <v>0.1834341412358438</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5834194946220184</v>
+        <v>0.5765557358617593</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2350940245956636</v>
+        <v>0.2366440245956635</v>
       </c>
       <c r="C87">
-        <v>-504.1700587128055</v>
+        <v>-527.0359443493514</v>
       </c>
       <c r="D87">
-        <v>623.6149412871943</v>
+        <v>618.5500556506486</v>
       </c>
       <c r="E87">
-        <v>820.9849999999998</v>
+        <v>838.7859999999999</v>
       </c>
       <c r="F87">
-        <v>1513.085</v>
+        <v>1530.886</v>
       </c>
       <c r="G87">
         <v>385.3</v>
@@ -8421,37 +8421,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M87">
-        <v>303.827468</v>
+        <v>307.4019088</v>
       </c>
       <c r="N87">
-        <v>-128.6539986122448</v>
+        <v>-132.2284394122449</v>
       </c>
       <c r="O87">
-        <v>-19.29809979183672</v>
+        <v>-19.83426591183673</v>
       </c>
       <c r="P87">
-        <v>-109.3558988204081</v>
+        <v>-112.3941735004082</v>
       </c>
       <c r="Q87">
-        <v>149.1441011795919</v>
+        <v>146.1058264995918</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5278333636346421</v>
+        <v>0.5622643181799737</v>
       </c>
       <c r="T87">
-        <v>5.774635488171727</v>
+        <v>6.187109451612565</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08648336037926389</v>
+        <v>0.08547773990973757</v>
       </c>
       <c r="W87">
-        <v>0.1834341412358438</v>
+        <v>0.1836360698261247</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5765557358617593</v>
+        <v>0.5698515993982505</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2366440245956635</v>
+        <v>0.2381940245956636</v>
       </c>
       <c r="C88">
-        <v>-527.0359443493514</v>
+        <v>-549.8202206661363</v>
       </c>
       <c r="D88">
-        <v>618.5500556506486</v>
+        <v>613.5667793338636</v>
       </c>
       <c r="E88">
-        <v>838.7859999999999</v>
+        <v>856.5869999999999</v>
       </c>
       <c r="F88">
-        <v>1530.886</v>
+        <v>1548.687</v>
       </c>
       <c r="G88">
         <v>385.3</v>
@@ -8503,37 +8503,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M88">
-        <v>307.4019088</v>
+        <v>310.9763496</v>
       </c>
       <c r="N88">
-        <v>-132.2284394122449</v>
+        <v>-135.8028802122449</v>
       </c>
       <c r="O88">
-        <v>-19.83426591183673</v>
+        <v>-20.37043203183673</v>
       </c>
       <c r="P88">
-        <v>-112.3941735004082</v>
+        <v>-115.4324481804081</v>
       </c>
       <c r="Q88">
-        <v>146.1058264995918</v>
+        <v>143.0675518195919</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5622643181799737</v>
+        <v>0.6019923426553563</v>
       </c>
       <c r="T88">
-        <v>6.187109451612565</v>
+        <v>6.663040947890455</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08547773990973757</v>
+        <v>0.08449523715215439</v>
       </c>
       <c r="W88">
-        <v>0.1836360698261247</v>
+        <v>0.1838333563798474</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5698515993982505</v>
+        <v>0.5633015810143625</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2381940245956636</v>
+        <v>0.2397440245956636</v>
       </c>
       <c r="C89">
-        <v>-549.8202206661363</v>
+        <v>-572.5248443273972</v>
       </c>
       <c r="D89">
-        <v>613.5667793338636</v>
+        <v>608.6631556726026</v>
       </c>
       <c r="E89">
-        <v>856.5869999999999</v>
+        <v>874.3879999999998</v>
       </c>
       <c r="F89">
-        <v>1548.687</v>
+        <v>1566.488</v>
       </c>
       <c r="G89">
         <v>385.3</v>
@@ -8585,37 +8585,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M89">
-        <v>310.9763496</v>
+        <v>314.5507904</v>
       </c>
       <c r="N89">
-        <v>-135.8028802122449</v>
+        <v>-139.3773210122449</v>
       </c>
       <c r="O89">
-        <v>-20.37043203183673</v>
+        <v>-20.90659815183673</v>
       </c>
       <c r="P89">
-        <v>-115.4324481804081</v>
+        <v>-118.4707228604081</v>
       </c>
       <c r="Q89">
-        <v>143.0675518195919</v>
+        <v>140.0292771395919</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6019923426553563</v>
+        <v>0.6483417045433028</v>
       </c>
       <c r="T89">
-        <v>6.663040947890455</v>
+        <v>7.21829436021466</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08449523715215439</v>
+        <v>0.08353506400269808</v>
       </c>
       <c r="W89">
-        <v>0.1838333563798474</v>
+        <v>0.1840261591482582</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5633015810143625</v>
+        <v>0.5569004266846539</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2397440245956636</v>
+        <v>0.2412940245956636</v>
       </c>
       <c r="C90">
-        <v>-572.5248443273972</v>
+        <v>-595.151709942696</v>
       </c>
       <c r="D90">
-        <v>608.6631556726026</v>
+        <v>603.837290057304</v>
       </c>
       <c r="E90">
-        <v>874.3879999999998</v>
+        <v>892.189</v>
       </c>
       <c r="F90">
-        <v>1566.488</v>
+        <v>1584.289</v>
       </c>
       <c r="G90">
         <v>385.3</v>
@@ -8667,37 +8667,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M90">
-        <v>314.5507904</v>
+        <v>318.1252312</v>
       </c>
       <c r="N90">
-        <v>-139.3773210122449</v>
+        <v>-142.9517618122449</v>
       </c>
       <c r="O90">
-        <v>-20.90659815183673</v>
+        <v>-21.44276427183674</v>
       </c>
       <c r="P90">
-        <v>-118.4707228604081</v>
+        <v>-121.5089975404082</v>
       </c>
       <c r="Q90">
-        <v>140.0292771395919</v>
+        <v>136.9910024595918</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6483417045433028</v>
+        <v>0.7031182231381484</v>
       </c>
       <c r="T90">
-        <v>7.21829436021466</v>
+        <v>7.874502938415993</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08353506400269808</v>
+        <v>0.08259646777794864</v>
       </c>
       <c r="W90">
-        <v>0.1840261591482582</v>
+        <v>0.1842146292701879</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5569004266846539</v>
+        <v>0.5506431185196576</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2412940245956636</v>
+        <v>0.2428440245956636</v>
       </c>
       <c r="C91">
-        <v>-595.151709942696</v>
+        <v>-617.7026525076094</v>
       </c>
       <c r="D91">
-        <v>603.837290057304</v>
+        <v>599.0873474923904</v>
       </c>
       <c r="E91">
-        <v>892.189</v>
+        <v>909.9899999999999</v>
       </c>
       <c r="F91">
-        <v>1584.289</v>
+        <v>1602.09</v>
       </c>
       <c r="G91">
         <v>385.3</v>
@@ -8749,37 +8749,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M91">
-        <v>318.1252312</v>
+        <v>321.699672</v>
       </c>
       <c r="N91">
-        <v>-142.9517618122449</v>
+        <v>-146.5262026122449</v>
       </c>
       <c r="O91">
-        <v>-21.44276427183674</v>
+        <v>-21.97893039183673</v>
       </c>
       <c r="P91">
-        <v>-121.5089975404082</v>
+        <v>-124.5472722204082</v>
       </c>
       <c r="Q91">
-        <v>136.9910024595918</v>
+        <v>133.9527277795918</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7031182231381484</v>
+        <v>0.7688500454519633</v>
       </c>
       <c r="T91">
-        <v>7.874502938415993</v>
+        <v>8.661953232257593</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08259646777794864</v>
+        <v>0.08167872924708255</v>
       </c>
       <c r="W91">
-        <v>0.1842146292701879</v>
+        <v>0.1843989111671858</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5506431185196576</v>
+        <v>0.5445248616472171</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2428440245956636</v>
+        <v>0.2443940245956636</v>
       </c>
       <c r="C92">
-        <v>-617.7026525076094</v>
+        <v>-640.1794497301282</v>
       </c>
       <c r="D92">
-        <v>599.0873474923904</v>
+        <v>594.4115502698718</v>
       </c>
       <c r="E92">
-        <v>909.9899999999999</v>
+        <v>927.7910000000001</v>
       </c>
       <c r="F92">
-        <v>1602.09</v>
+        <v>1619.891</v>
       </c>
       <c r="G92">
         <v>385.3</v>
@@ -8831,37 +8831,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M92">
-        <v>321.699672</v>
+        <v>325.2741128</v>
       </c>
       <c r="N92">
-        <v>-146.5262026122449</v>
+        <v>-150.1006434122449</v>
       </c>
       <c r="O92">
-        <v>-21.97893039183673</v>
+        <v>-22.51509651183673</v>
       </c>
       <c r="P92">
-        <v>-124.5472722204082</v>
+        <v>-127.5855469004082</v>
       </c>
       <c r="Q92">
-        <v>133.9527277795918</v>
+        <v>130.9144530995918</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7688500454519633</v>
+        <v>0.8491889393910704</v>
       </c>
       <c r="T92">
-        <v>8.661953232257593</v>
+        <v>9.624392480286215</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08167872924708255</v>
+        <v>0.0807811607938179</v>
       </c>
       <c r="W92">
-        <v>0.1843989111671858</v>
+        <v>0.1845791429126014</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5445248616472171</v>
+        <v>0.5385410719587862</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2443940245956636</v>
+        <v>0.2459440245956636</v>
       </c>
       <c r="C93">
-        <v>-640.1794497301282</v>
+        <v>-662.583824248951</v>
       </c>
       <c r="D93">
-        <v>594.4115502698718</v>
+        <v>589.808175751049</v>
       </c>
       <c r="E93">
-        <v>927.7910000000001</v>
+        <v>945.592</v>
       </c>
       <c r="F93">
-        <v>1619.891</v>
+        <v>1637.692</v>
       </c>
       <c r="G93">
         <v>385.3</v>
@@ -8913,37 +8913,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M93">
-        <v>325.2741128</v>
+        <v>328.8485536</v>
       </c>
       <c r="N93">
-        <v>-150.1006434122449</v>
+        <v>-153.6750842122449</v>
       </c>
       <c r="O93">
-        <v>-22.51509651183673</v>
+        <v>-23.05126263183673</v>
       </c>
       <c r="P93">
-        <v>-127.5855469004082</v>
+        <v>-130.6238215804082</v>
       </c>
       <c r="Q93">
-        <v>130.9144530995918</v>
+        <v>127.8761784195918</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8491889393910704</v>
+        <v>0.9496125568149545</v>
       </c>
       <c r="T93">
-        <v>9.624392480286215</v>
+        <v>10.827441540322</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0807811607938179</v>
+        <v>0.07990310469823295</v>
       </c>
       <c r="W93">
-        <v>0.1845791429126014</v>
+        <v>0.1847554565765948</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5385410719587862</v>
+        <v>0.5326873646548863</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2459440245956636</v>
+        <v>0.2474940245956636</v>
       </c>
       <c r="C94">
-        <v>-662.583824248951</v>
+        <v>-684.9174457494978</v>
       </c>
       <c r="D94">
-        <v>589.808175751049</v>
+        <v>585.2755542505022</v>
       </c>
       <c r="E94">
-        <v>945.592</v>
+        <v>963.3929999999999</v>
       </c>
       <c r="F94">
-        <v>1637.692</v>
+        <v>1655.493</v>
       </c>
       <c r="G94">
         <v>385.3</v>
@@ -8995,37 +8995,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M94">
-        <v>328.8485536</v>
+        <v>332.4229944</v>
       </c>
       <c r="N94">
-        <v>-153.6750842122449</v>
+        <v>-157.2495250122449</v>
       </c>
       <c r="O94">
-        <v>-23.05126263183673</v>
+        <v>-23.58742875183673</v>
       </c>
       <c r="P94">
-        <v>-130.6238215804082</v>
+        <v>-133.6620962604081</v>
       </c>
       <c r="Q94">
-        <v>127.8761784195918</v>
+        <v>124.8379037395919</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9496125568149545</v>
+        <v>1.078728636359948</v>
       </c>
       <c r="T94">
-        <v>10.827441540322</v>
+        <v>12.37421890322514</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.07990310469823295</v>
+        <v>0.07904393152943474</v>
       </c>
       <c r="W94">
-        <v>0.1847554565765948</v>
+        <v>0.1849279785488895</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5326873646548863</v>
+        <v>0.5269595435295649</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2474940245956636</v>
+        <v>0.2490440245956636</v>
       </c>
       <c r="C95">
-        <v>-684.9174457494978</v>
+        <v>-707.1819329830982</v>
       </c>
       <c r="D95">
-        <v>585.2755542505022</v>
+        <v>580.8120670169019</v>
       </c>
       <c r="E95">
-        <v>963.3929999999999</v>
+        <v>981.1940000000001</v>
       </c>
       <c r="F95">
-        <v>1655.493</v>
+        <v>1673.294</v>
       </c>
       <c r="G95">
         <v>385.3</v>
@@ -9077,37 +9077,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M95">
-        <v>332.4229944</v>
+        <v>335.9974352</v>
       </c>
       <c r="N95">
-        <v>-157.2495250122449</v>
+        <v>-160.8239658122449</v>
       </c>
       <c r="O95">
-        <v>-23.58742875183673</v>
+        <v>-24.12359487183674</v>
       </c>
       <c r="P95">
-        <v>-133.6620962604081</v>
+        <v>-136.7003709404082</v>
       </c>
       <c r="Q95">
-        <v>124.8379037395919</v>
+        <v>121.7996290595918</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.078728636359948</v>
+        <v>1.250883409086607</v>
       </c>
       <c r="T95">
-        <v>12.37421890322514</v>
+        <v>14.43658872042933</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07904393152943474</v>
+        <v>0.07820303864082372</v>
       </c>
       <c r="W95">
-        <v>0.1849279785488895</v>
+        <v>0.1850968298409226</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5269595435295649</v>
+        <v>0.5213535909388248</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2490440245956636</v>
+        <v>0.2505940245956636</v>
       </c>
       <c r="C96">
-        <v>-707.1819329830982</v>
+        <v>-729.3788556944839</v>
       </c>
       <c r="D96">
-        <v>580.8120670169019</v>
+        <v>576.416144305516</v>
       </c>
       <c r="E96">
-        <v>981.1940000000001</v>
+        <v>998.995</v>
       </c>
       <c r="F96">
-        <v>1673.294</v>
+        <v>1691.095</v>
       </c>
       <c r="G96">
         <v>385.3</v>
@@ -9159,37 +9159,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M96">
-        <v>335.9974352</v>
+        <v>339.571876</v>
       </c>
       <c r="N96">
-        <v>-160.8239658122449</v>
+        <v>-164.3984066122449</v>
       </c>
       <c r="O96">
-        <v>-24.12359487183674</v>
+        <v>-24.65976099183674</v>
       </c>
       <c r="P96">
-        <v>-136.7003709404082</v>
+        <v>-139.7386456204082</v>
       </c>
       <c r="Q96">
-        <v>121.7996290595918</v>
+        <v>118.7613543795918</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.250883409086607</v>
+        <v>1.491900090903928</v>
       </c>
       <c r="T96">
-        <v>14.43658872042933</v>
+        <v>17.3239064645152</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07820303864082372</v>
+        <v>0.077379848760394</v>
       </c>
       <c r="W96">
-        <v>0.1850968298409226</v>
+        <v>0.1852621263689129</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5213535909388248</v>
+        <v>0.5158656584026267</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2505940245956636</v>
+        <v>0.2521440245956636</v>
       </c>
       <c r="C97">
-        <v>-729.3788556944839</v>
+        <v>-751.5097364624116</v>
       </c>
       <c r="D97">
-        <v>576.416144305516</v>
+        <v>572.0862635375884</v>
       </c>
       <c r="E97">
-        <v>998.995</v>
+        <v>1016.796</v>
       </c>
       <c r="F97">
-        <v>1691.095</v>
+        <v>1708.896</v>
       </c>
       <c r="G97">
         <v>385.3</v>
@@ -9241,37 +9241,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M97">
-        <v>339.571876</v>
+        <v>343.1463168</v>
       </c>
       <c r="N97">
-        <v>-164.3984066122449</v>
+        <v>-167.9728474122449</v>
       </c>
       <c r="O97">
-        <v>-24.65976099183674</v>
+        <v>-25.19592711183673</v>
       </c>
       <c r="P97">
-        <v>-139.7386456204082</v>
+        <v>-142.7769203004082</v>
       </c>
       <c r="Q97">
-        <v>118.7613543795918</v>
+        <v>115.7230796995918</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.491900090903928</v>
+        <v>1.853425113629912</v>
       </c>
       <c r="T97">
-        <v>17.3239064645152</v>
+        <v>21.65488308064402</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.077379848760394</v>
+        <v>0.07657380866913989</v>
       </c>
       <c r="W97">
-        <v>0.1852621263689129</v>
+        <v>0.1854239792192367</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5158656584026267</v>
+        <v>0.510492057794266</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2521440245956636</v>
+        <v>0.2536940245956635</v>
       </c>
       <c r="C98">
-        <v>-751.5097364624116</v>
+        <v>-773.5760524579428</v>
       </c>
       <c r="D98">
-        <v>572.0862635375884</v>
+        <v>567.8209475420572</v>
       </c>
       <c r="E98">
-        <v>1016.796</v>
+        <v>1034.597</v>
       </c>
       <c r="F98">
-        <v>1708.896</v>
+        <v>1726.697</v>
       </c>
       <c r="G98">
         <v>385.3</v>
@@ -9323,37 +9323,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M98">
-        <v>343.1463168</v>
+        <v>346.7207576</v>
       </c>
       <c r="N98">
-        <v>-167.9728474122449</v>
+        <v>-171.5472882122449</v>
       </c>
       <c r="O98">
-        <v>-25.19592711183673</v>
+        <v>-25.73209323183673</v>
       </c>
       <c r="P98">
-        <v>-142.7769203004082</v>
+        <v>-145.8151949804082</v>
       </c>
       <c r="Q98">
-        <v>115.7230796995918</v>
+        <v>112.6848050195918</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.853425113629906</v>
+        <v>2.455966818173208</v>
       </c>
       <c r="T98">
-        <v>21.65488308064396</v>
+        <v>28.87317744085861</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07657380866913989</v>
+        <v>0.07578438796121063</v>
       </c>
       <c r="W98">
-        <v>0.1854239792192367</v>
+        <v>0.1855824948973889</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.510492057794266</v>
+        <v>0.5052292530747375</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2536940245956635</v>
+        <v>0.2552440245956636</v>
       </c>
       <c r="C99">
-        <v>-773.5760524579428</v>
+        <v>-795.5792371246539</v>
       </c>
       <c r="D99">
-        <v>567.8209475420572</v>
+        <v>563.6187628753459</v>
       </c>
       <c r="E99">
-        <v>1034.597</v>
+        <v>1052.398</v>
       </c>
       <c r="F99">
-        <v>1726.697</v>
+        <v>1744.498</v>
       </c>
       <c r="G99">
         <v>385.3</v>
@@ -9405,37 +9405,37 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M99">
-        <v>346.7207576</v>
+        <v>350.2951983999999</v>
       </c>
       <c r="N99">
-        <v>-171.5472882122449</v>
+        <v>-175.1217290122448</v>
       </c>
       <c r="O99">
-        <v>-25.73209323183673</v>
+        <v>-26.26825935183672</v>
       </c>
       <c r="P99">
-        <v>-145.8151949804082</v>
+        <v>-148.8534696604081</v>
       </c>
       <c r="Q99">
-        <v>112.6848050195918</v>
+        <v>109.6465303395919</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.455966818173208</v>
+        <v>3.661050227259814</v>
       </c>
       <c r="T99">
-        <v>28.87317744085861</v>
+        <v>43.30976616128793</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07578438796121063</v>
+        <v>0.07501107787997378</v>
       </c>
       <c r="W99">
-        <v>0.1855824948973889</v>
+        <v>0.1857377755617013</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5052292530747375</v>
+        <v>0.5000738525331586</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2552440245956636</v>
+        <v>0.2922955620373487</v>
       </c>
       <c r="C100">
-        <v>-795.5792371246539</v>
+        <v>-898.0995786126277</v>
       </c>
       <c r="D100">
-        <v>563.6187628753459</v>
+        <v>478.8994213873723</v>
       </c>
       <c r="E100">
-        <v>1052.398</v>
+        <v>1070.199</v>
       </c>
       <c r="F100">
-        <v>1744.498</v>
+        <v>1762.299</v>
       </c>
       <c r="G100">
         <v>385.3</v>
@@ -9487,129 +9487,47 @@
         <v>175.1734693877551</v>
       </c>
       <c r="M100">
-        <v>350.2951983999999</v>
+        <v>415.5501042</v>
       </c>
       <c r="N100">
-        <v>-175.1217290122448</v>
+        <v>-240.3766348122449</v>
       </c>
       <c r="O100">
-        <v>-26.26825935183672</v>
+        <v>-36.05649522183673</v>
       </c>
       <c r="P100">
-        <v>-148.8534696604081</v>
+        <v>-204.3201395904082</v>
       </c>
       <c r="Q100">
-        <v>109.6465303395919</v>
+        <v>54.17986040959184</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.661050227259814</v>
+        <v>7.361454198688146</v>
       </c>
       <c r="T100">
-        <v>43.30976616128793</v>
+        <v>87.63965223568405</v>
       </c>
       <c r="U100">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07501107787997378</v>
+        <v>0.06323189464420609</v>
       </c>
       <c r="W100">
-        <v>0.1857377755617013</v>
+        <v>0.2208899192428962</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5000738525331586</v>
+        <v>0.4215459642947074</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2922955620373487</v>
-      </c>
-      <c r="C101">
-        <v>-898.0995786126277</v>
-      </c>
-      <c r="D101">
-        <v>478.8994213873723</v>
-      </c>
-      <c r="E101">
-        <v>1070.199</v>
-      </c>
-      <c r="F101">
-        <v>1762.299</v>
-      </c>
-      <c r="G101">
-        <v>385.3</v>
-      </c>
-      <c r="H101">
-        <v>1088</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>433.6734693877551</v>
-      </c>
-      <c r="K101">
-        <v>258.5</v>
-      </c>
-      <c r="L101">
-        <v>175.1734693877551</v>
-      </c>
-      <c r="M101">
-        <v>415.5501042</v>
-      </c>
-      <c r="N101">
-        <v>-240.3766348122449</v>
-      </c>
-      <c r="O101">
-        <v>-36.05649522183673</v>
-      </c>
-      <c r="P101">
-        <v>-204.3201395904082</v>
-      </c>
-      <c r="Q101">
-        <v>54.17986040959184</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.361454198688146</v>
-      </c>
-      <c r="T101">
-        <v>87.63965223568405</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06323189464420609</v>
-      </c>
-      <c r="W101">
-        <v>0.2208899192428962</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4215459642947074</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
